--- a/InputData/elec/EIaE/Elec Imports and Exports.xlsx
+++ b/InputData/elec/EIaE/Elec Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\EIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECA30A8-2CCE-4178-A4B5-03C41ACCD92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0911969-E135-413A-9172-843F213954D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37050" yWindow="1065" windowWidth="22785" windowHeight="14115" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39510" yWindow="3135" windowWidth="23460" windowHeight="12165" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,9 @@
     <sheet name="EIaE-BIE" sheetId="3" r:id="rId8"/>
     <sheet name="EIaE-BEE" sheetId="5" r:id="rId9"/>
     <sheet name="EIaE-IEP" sheetId="9" r:id="rId10"/>
-    <sheet name="EIaE-BEEP" sheetId="10" r:id="rId11"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="lignite_multiplier">'[1]Hard Coal and Lig Multipliers'!$N$16</definedName>
@@ -53,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="267">
   <si>
     <t>EIaE BAU Imported Electricity</t>
   </si>
@@ -855,9 +854,6 @@
   <si>
     <t>Imported Electricity Price</t>
   </si>
-  <si>
-    <t>Exported Electricity Price</t>
-  </si>
 </sst>
 </file>
 
@@ -1135,7 +1131,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1260,12 +1256,11 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="35" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="37"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="33" applyFont="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="5" applyFont="1">
       <alignment wrapText="1"/>
@@ -1374,7 +1369,18 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5">
+        <row r="16">
+          <cell r="N16">
+            <v>0.92062879123815489</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="N17">
+            <v>1.0036394752510358</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
@@ -1776,7 +1782,7 @@
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2129,390 +2135,6 @@
     <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>266</v>
-      </c>
-      <c r="B2" s="12">
-        <f>INDEX('AEO Table 3 2021'!67:67,MATCH(B1,'AEO Table 3 2021'!1:1,0))/10^6*About!$A$60/About!$A$59</f>
-        <v>92.385094561027103</v>
-      </c>
-      <c r="C2" s="12">
-        <f>INDEX('AEO Table 3 2022'!67:67,MATCH(C1,'AEO Table 3 2022'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>93.978105887781467</v>
-      </c>
-      <c r="D2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(D1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>103.57699495763774</v>
-      </c>
-      <c r="E2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(E1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>100.93588062916164</v>
-      </c>
-      <c r="F2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(F1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>97.195681889697426</v>
-      </c>
-      <c r="G2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(G1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>93.454633244350902</v>
-      </c>
-      <c r="H2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(H1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>91.239535684800543</v>
-      </c>
-      <c r="I2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(I1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>89.660948251027904</v>
-      </c>
-      <c r="J2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(J1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>88.539575491901672</v>
-      </c>
-      <c r="K2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(K1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>88.110797974276579</v>
-      </c>
-      <c r="L2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(L1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>88.231022075751014</v>
-      </c>
-      <c r="M2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(M1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>88.512956670934656</v>
-      </c>
-      <c r="N2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(N1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>88.751158694051711</v>
-      </c>
-      <c r="O2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(O1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>90.059794049246733</v>
-      </c>
-      <c r="P2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(P1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>90.906762841840404</v>
-      </c>
-      <c r="Q2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(Q1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>90.916799825593372</v>
-      </c>
-      <c r="R2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(R1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>91.448921851336408</v>
-      </c>
-      <c r="S2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(S1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>92.108836188077319</v>
-      </c>
-      <c r="T2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(T1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>93.096134848851065</v>
-      </c>
-      <c r="U2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(U1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>93.863484227123067</v>
-      </c>
-      <c r="V2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(V1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>94.514613312243782</v>
-      </c>
-      <c r="W2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(W1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.041439325822225</v>
-      </c>
-      <c r="X2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(X1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.257879133013986</v>
-      </c>
-      <c r="Y2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(Y1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.38822694333146</v>
-      </c>
-      <c r="Z2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(Z1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.496329768055801</v>
-      </c>
-      <c r="AA2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AA1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.584783578215337</v>
-      </c>
-      <c r="AB2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AB1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>95.294534937734014</v>
-      </c>
-      <c r="AC2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AC1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>94.861984878692553</v>
-      </c>
-      <c r="AD2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AD1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>94.713022973217988</v>
-      </c>
-      <c r="AE2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AE1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>94.189483840551745</v>
-      </c>
-      <c r="AF2" s="12">
-        <f>INDEX('AEO Table 3 2023'!67:67,MATCH(AF1,'AEO Table 3 2023'!1:1,0))/10^6*About!$A$61/About!$A$59</f>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AG2" s="12">
-        <f>AF2</f>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AH2" s="12">
-        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AI2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AJ2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AK2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AL2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AM2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AN2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AO2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AP2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AQ2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AR2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AS2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AT2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AU2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AV2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AW2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AX2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AY2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-      <c r="AZ2" s="12">
-        <f t="shared" si="0"/>
-        <v>93.402132765682126</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364777A9-21C3-491A-80BE-AFAA838DFA2A}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AZ2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="B1">
-        <v>2020</v>
-      </c>
-      <c r="C1">
-        <v>2021</v>
-      </c>
-      <c r="D1">
-        <v>2022</v>
-      </c>
-      <c r="E1">
-        <v>2023</v>
-      </c>
-      <c r="F1">
-        <v>2024</v>
-      </c>
-      <c r="G1">
-        <v>2025</v>
-      </c>
-      <c r="H1">
-        <v>2026</v>
-      </c>
-      <c r="I1">
-        <v>2027</v>
-      </c>
-      <c r="J1">
-        <v>2028</v>
-      </c>
-      <c r="K1">
-        <v>2029</v>
-      </c>
-      <c r="L1">
-        <v>2030</v>
-      </c>
-      <c r="M1">
-        <v>2031</v>
-      </c>
-      <c r="N1">
-        <v>2032</v>
-      </c>
-      <c r="O1">
-        <v>2033</v>
-      </c>
-      <c r="P1">
-        <v>2034</v>
-      </c>
-      <c r="Q1">
-        <v>2035</v>
-      </c>
-      <c r="R1">
-        <v>2036</v>
-      </c>
-      <c r="S1">
-        <v>2037</v>
-      </c>
-      <c r="T1">
-        <v>2038</v>
-      </c>
-      <c r="U1">
-        <v>2039</v>
-      </c>
-      <c r="V1">
-        <v>2040</v>
-      </c>
-      <c r="W1">
-        <v>2041</v>
-      </c>
-      <c r="X1">
-        <v>2042</v>
-      </c>
-      <c r="Y1">
-        <v>2043</v>
-      </c>
-      <c r="Z1">
-        <v>2044</v>
-      </c>
-      <c r="AA1">
-        <v>2045</v>
-      </c>
-      <c r="AB1">
-        <v>2046</v>
-      </c>
-      <c r="AC1">
-        <v>2047</v>
-      </c>
-      <c r="AD1">
-        <v>2048</v>
-      </c>
-      <c r="AE1">
-        <v>2049</v>
-      </c>
-      <c r="AF1">
-        <v>2050</v>
-      </c>
-      <c r="AG1">
-        <v>2051</v>
-      </c>
-      <c r="AH1">
-        <v>2052</v>
-      </c>
-      <c r="AI1">
-        <v>2053</v>
-      </c>
-      <c r="AJ1">
-        <v>2054</v>
-      </c>
-      <c r="AK1">
-        <v>2055</v>
-      </c>
-      <c r="AL1">
-        <v>2056</v>
-      </c>
-      <c r="AM1">
-        <v>2057</v>
-      </c>
-      <c r="AN1">
-        <v>2058</v>
-      </c>
-      <c r="AO1">
-        <v>2059</v>
-      </c>
-      <c r="AP1">
-        <v>2060</v>
-      </c>
-      <c r="AQ1">
-        <v>2061</v>
-      </c>
-      <c r="AR1">
-        <v>2062</v>
-      </c>
-      <c r="AS1">
-        <v>2063</v>
-      </c>
-      <c r="AT1">
-        <v>2064</v>
-      </c>
-      <c r="AU1">
-        <v>2065</v>
-      </c>
-      <c r="AV1">
-        <v>2066</v>
-      </c>
-      <c r="AW1">
-        <v>2067</v>
-      </c>
-      <c r="AX1">
-        <v>2068</v>
-      </c>
-      <c r="AY1">
-        <v>2069</v>
-      </c>
-      <c r="AZ1">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>267</v>
       </c>
       <c r="B2" s="12">
         <f>INDEX('AEO Table 3 2021'!67:67,MATCH(B1,'AEO Table 3 2021'!1:1,0))/10^6*About!$A$60/About!$A$59</f>
@@ -16527,37 +16149,37 @@
       <c r="AF307" s="34"/>
     </row>
     <row r="308" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B308" s="61"/>
-      <c r="C308" s="61"/>
-      <c r="D308" s="61"/>
-      <c r="E308" s="61"/>
-      <c r="F308" s="61"/>
-      <c r="G308" s="61"/>
-      <c r="H308" s="61"/>
-      <c r="I308" s="61"/>
-      <c r="J308" s="61"/>
-      <c r="K308" s="61"/>
-      <c r="L308" s="61"/>
-      <c r="M308" s="61"/>
-      <c r="N308" s="61"/>
-      <c r="O308" s="61"/>
-      <c r="P308" s="61"/>
-      <c r="Q308" s="61"/>
-      <c r="R308" s="61"/>
-      <c r="S308" s="61"/>
-      <c r="T308" s="61"/>
-      <c r="U308" s="61"/>
-      <c r="V308" s="61"/>
-      <c r="W308" s="61"/>
-      <c r="X308" s="61"/>
-      <c r="Y308" s="61"/>
-      <c r="Z308" s="61"/>
-      <c r="AA308" s="61"/>
-      <c r="AB308" s="61"/>
-      <c r="AC308" s="61"/>
-      <c r="AD308" s="61"/>
-      <c r="AE308" s="61"/>
-      <c r="AF308" s="61"/>
+      <c r="B308" s="58"/>
+      <c r="C308" s="58"/>
+      <c r="D308" s="58"/>
+      <c r="E308" s="58"/>
+      <c r="F308" s="58"/>
+      <c r="G308" s="58"/>
+      <c r="H308" s="58"/>
+      <c r="I308" s="58"/>
+      <c r="J308" s="58"/>
+      <c r="K308" s="58"/>
+      <c r="L308" s="58"/>
+      <c r="M308" s="58"/>
+      <c r="N308" s="58"/>
+      <c r="O308" s="58"/>
+      <c r="P308" s="58"/>
+      <c r="Q308" s="58"/>
+      <c r="R308" s="58"/>
+      <c r="S308" s="58"/>
+      <c r="T308" s="58"/>
+      <c r="U308" s="58"/>
+      <c r="V308" s="58"/>
+      <c r="W308" s="58"/>
+      <c r="X308" s="58"/>
+      <c r="Y308" s="58"/>
+      <c r="Z308" s="58"/>
+      <c r="AA308" s="58"/>
+      <c r="AB308" s="58"/>
+      <c r="AC308" s="58"/>
+      <c r="AD308" s="58"/>
+      <c r="AE308" s="58"/>
+      <c r="AF308" s="58"/>
     </row>
     <row r="309" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="310" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -16814,37 +16436,37 @@
       <c r="AF510" s="34"/>
     </row>
     <row r="511" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B511" s="61"/>
-      <c r="C511" s="61"/>
-      <c r="D511" s="61"/>
-      <c r="E511" s="61"/>
-      <c r="F511" s="61"/>
-      <c r="G511" s="61"/>
-      <c r="H511" s="61"/>
-      <c r="I511" s="61"/>
-      <c r="J511" s="61"/>
-      <c r="K511" s="61"/>
-      <c r="L511" s="61"/>
-      <c r="M511" s="61"/>
-      <c r="N511" s="61"/>
-      <c r="O511" s="61"/>
-      <c r="P511" s="61"/>
-      <c r="Q511" s="61"/>
-      <c r="R511" s="61"/>
-      <c r="S511" s="61"/>
-      <c r="T511" s="61"/>
-      <c r="U511" s="61"/>
-      <c r="V511" s="61"/>
-      <c r="W511" s="61"/>
-      <c r="X511" s="61"/>
-      <c r="Y511" s="61"/>
-      <c r="Z511" s="61"/>
-      <c r="AA511" s="61"/>
-      <c r="AB511" s="61"/>
-      <c r="AC511" s="61"/>
-      <c r="AD511" s="61"/>
-      <c r="AE511" s="61"/>
-      <c r="AF511" s="61"/>
+      <c r="B511" s="58"/>
+      <c r="C511" s="58"/>
+      <c r="D511" s="58"/>
+      <c r="E511" s="58"/>
+      <c r="F511" s="58"/>
+      <c r="G511" s="58"/>
+      <c r="H511" s="58"/>
+      <c r="I511" s="58"/>
+      <c r="J511" s="58"/>
+      <c r="K511" s="58"/>
+      <c r="L511" s="58"/>
+      <c r="M511" s="58"/>
+      <c r="N511" s="58"/>
+      <c r="O511" s="58"/>
+      <c r="P511" s="58"/>
+      <c r="Q511" s="58"/>
+      <c r="R511" s="58"/>
+      <c r="S511" s="58"/>
+      <c r="T511" s="58"/>
+      <c r="U511" s="58"/>
+      <c r="V511" s="58"/>
+      <c r="W511" s="58"/>
+      <c r="X511" s="58"/>
+      <c r="Y511" s="58"/>
+      <c r="Z511" s="58"/>
+      <c r="AA511" s="58"/>
+      <c r="AB511" s="58"/>
+      <c r="AC511" s="58"/>
+      <c r="AD511" s="58"/>
+      <c r="AE511" s="58"/>
+      <c r="AF511" s="58"/>
     </row>
     <row r="512" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="513" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -17017,37 +16639,37 @@
       <c r="AF711" s="34"/>
     </row>
     <row r="712" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B712" s="61"/>
-      <c r="C712" s="61"/>
-      <c r="D712" s="61"/>
-      <c r="E712" s="61"/>
-      <c r="F712" s="61"/>
-      <c r="G712" s="61"/>
-      <c r="H712" s="61"/>
-      <c r="I712" s="61"/>
-      <c r="J712" s="61"/>
-      <c r="K712" s="61"/>
-      <c r="L712" s="61"/>
-      <c r="M712" s="61"/>
-      <c r="N712" s="61"/>
-      <c r="O712" s="61"/>
-      <c r="P712" s="61"/>
-      <c r="Q712" s="61"/>
-      <c r="R712" s="61"/>
-      <c r="S712" s="61"/>
-      <c r="T712" s="61"/>
-      <c r="U712" s="61"/>
-      <c r="V712" s="61"/>
-      <c r="W712" s="61"/>
-      <c r="X712" s="61"/>
-      <c r="Y712" s="61"/>
-      <c r="Z712" s="61"/>
-      <c r="AA712" s="61"/>
-      <c r="AB712" s="61"/>
-      <c r="AC712" s="61"/>
-      <c r="AD712" s="61"/>
-      <c r="AE712" s="61"/>
-      <c r="AF712" s="61"/>
+      <c r="B712" s="58"/>
+      <c r="C712" s="58"/>
+      <c r="D712" s="58"/>
+      <c r="E712" s="58"/>
+      <c r="F712" s="58"/>
+      <c r="G712" s="58"/>
+      <c r="H712" s="58"/>
+      <c r="I712" s="58"/>
+      <c r="J712" s="58"/>
+      <c r="K712" s="58"/>
+      <c r="L712" s="58"/>
+      <c r="M712" s="58"/>
+      <c r="N712" s="58"/>
+      <c r="O712" s="58"/>
+      <c r="P712" s="58"/>
+      <c r="Q712" s="58"/>
+      <c r="R712" s="58"/>
+      <c r="S712" s="58"/>
+      <c r="T712" s="58"/>
+      <c r="U712" s="58"/>
+      <c r="V712" s="58"/>
+      <c r="W712" s="58"/>
+      <c r="X712" s="58"/>
+      <c r="Y712" s="58"/>
+      <c r="Z712" s="58"/>
+      <c r="AA712" s="58"/>
+      <c r="AB712" s="58"/>
+      <c r="AC712" s="58"/>
+      <c r="AD712" s="58"/>
+      <c r="AE712" s="58"/>
+      <c r="AF712" s="58"/>
     </row>
     <row r="713" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="714" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -17202,37 +16824,37 @@
       <c r="AF886" s="34"/>
     </row>
     <row r="887" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B887" s="61"/>
-      <c r="C887" s="61"/>
-      <c r="D887" s="61"/>
-      <c r="E887" s="61"/>
-      <c r="F887" s="61"/>
-      <c r="G887" s="61"/>
-      <c r="H887" s="61"/>
-      <c r="I887" s="61"/>
-      <c r="J887" s="61"/>
-      <c r="K887" s="61"/>
-      <c r="L887" s="61"/>
-      <c r="M887" s="61"/>
-      <c r="N887" s="61"/>
-      <c r="O887" s="61"/>
-      <c r="P887" s="61"/>
-      <c r="Q887" s="61"/>
-      <c r="R887" s="61"/>
-      <c r="S887" s="61"/>
-      <c r="T887" s="61"/>
-      <c r="U887" s="61"/>
-      <c r="V887" s="61"/>
-      <c r="W887" s="61"/>
-      <c r="X887" s="61"/>
-      <c r="Y887" s="61"/>
-      <c r="Z887" s="61"/>
-      <c r="AA887" s="61"/>
-      <c r="AB887" s="61"/>
-      <c r="AC887" s="61"/>
-      <c r="AD887" s="61"/>
-      <c r="AE887" s="61"/>
-      <c r="AF887" s="61"/>
+      <c r="B887" s="58"/>
+      <c r="C887" s="58"/>
+      <c r="D887" s="58"/>
+      <c r="E887" s="58"/>
+      <c r="F887" s="58"/>
+      <c r="G887" s="58"/>
+      <c r="H887" s="58"/>
+      <c r="I887" s="58"/>
+      <c r="J887" s="58"/>
+      <c r="K887" s="58"/>
+      <c r="L887" s="58"/>
+      <c r="M887" s="58"/>
+      <c r="N887" s="58"/>
+      <c r="O887" s="58"/>
+      <c r="P887" s="58"/>
+      <c r="Q887" s="58"/>
+      <c r="R887" s="58"/>
+      <c r="S887" s="58"/>
+      <c r="T887" s="58"/>
+      <c r="U887" s="58"/>
+      <c r="V887" s="58"/>
+      <c r="W887" s="58"/>
+      <c r="X887" s="58"/>
+      <c r="Y887" s="58"/>
+      <c r="Z887" s="58"/>
+      <c r="AA887" s="58"/>
+      <c r="AB887" s="58"/>
+      <c r="AC887" s="58"/>
+      <c r="AD887" s="58"/>
+      <c r="AE887" s="58"/>
+      <c r="AF887" s="58"/>
     </row>
     <row r="888" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="889" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -17460,37 +17082,37 @@
       <c r="AF1100" s="34"/>
     </row>
     <row r="1101" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1101" s="61"/>
-      <c r="C1101" s="61"/>
-      <c r="D1101" s="61"/>
-      <c r="E1101" s="61"/>
-      <c r="F1101" s="61"/>
-      <c r="G1101" s="61"/>
-      <c r="H1101" s="61"/>
-      <c r="I1101" s="61"/>
-      <c r="J1101" s="61"/>
-      <c r="K1101" s="61"/>
-      <c r="L1101" s="61"/>
-      <c r="M1101" s="61"/>
-      <c r="N1101" s="61"/>
-      <c r="O1101" s="61"/>
-      <c r="P1101" s="61"/>
-      <c r="Q1101" s="61"/>
-      <c r="R1101" s="61"/>
-      <c r="S1101" s="61"/>
-      <c r="T1101" s="61"/>
-      <c r="U1101" s="61"/>
-      <c r="V1101" s="61"/>
-      <c r="W1101" s="61"/>
-      <c r="X1101" s="61"/>
-      <c r="Y1101" s="61"/>
-      <c r="Z1101" s="61"/>
-      <c r="AA1101" s="61"/>
-      <c r="AB1101" s="61"/>
-      <c r="AC1101" s="61"/>
-      <c r="AD1101" s="61"/>
-      <c r="AE1101" s="61"/>
-      <c r="AF1101" s="61"/>
+      <c r="B1101" s="58"/>
+      <c r="C1101" s="58"/>
+      <c r="D1101" s="58"/>
+      <c r="E1101" s="58"/>
+      <c r="F1101" s="58"/>
+      <c r="G1101" s="58"/>
+      <c r="H1101" s="58"/>
+      <c r="I1101" s="58"/>
+      <c r="J1101" s="58"/>
+      <c r="K1101" s="58"/>
+      <c r="L1101" s="58"/>
+      <c r="M1101" s="58"/>
+      <c r="N1101" s="58"/>
+      <c r="O1101" s="58"/>
+      <c r="P1101" s="58"/>
+      <c r="Q1101" s="58"/>
+      <c r="R1101" s="58"/>
+      <c r="S1101" s="58"/>
+      <c r="T1101" s="58"/>
+      <c r="U1101" s="58"/>
+      <c r="V1101" s="58"/>
+      <c r="W1101" s="58"/>
+      <c r="X1101" s="58"/>
+      <c r="Y1101" s="58"/>
+      <c r="Z1101" s="58"/>
+      <c r="AA1101" s="58"/>
+      <c r="AB1101" s="58"/>
+      <c r="AC1101" s="58"/>
+      <c r="AD1101" s="58"/>
+      <c r="AE1101" s="58"/>
+      <c r="AF1101" s="58"/>
     </row>
     <row r="1102" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1103" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -17611,37 +17233,37 @@
       <c r="AF1228" s="34"/>
     </row>
     <row r="1229" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1229" s="61"/>
-      <c r="C1229" s="61"/>
-      <c r="D1229" s="61"/>
-      <c r="E1229" s="61"/>
-      <c r="F1229" s="61"/>
-      <c r="G1229" s="61"/>
-      <c r="H1229" s="61"/>
-      <c r="I1229" s="61"/>
-      <c r="J1229" s="61"/>
-      <c r="K1229" s="61"/>
-      <c r="L1229" s="61"/>
-      <c r="M1229" s="61"/>
-      <c r="N1229" s="61"/>
-      <c r="O1229" s="61"/>
-      <c r="P1229" s="61"/>
-      <c r="Q1229" s="61"/>
-      <c r="R1229" s="61"/>
-      <c r="S1229" s="61"/>
-      <c r="T1229" s="61"/>
-      <c r="U1229" s="61"/>
-      <c r="V1229" s="61"/>
-      <c r="W1229" s="61"/>
-      <c r="X1229" s="61"/>
-      <c r="Y1229" s="61"/>
-      <c r="Z1229" s="61"/>
-      <c r="AA1229" s="61"/>
-      <c r="AB1229" s="61"/>
-      <c r="AC1229" s="61"/>
-      <c r="AD1229" s="61"/>
-      <c r="AE1229" s="61"/>
-      <c r="AF1229" s="61"/>
+      <c r="B1229" s="58"/>
+      <c r="C1229" s="58"/>
+      <c r="D1229" s="58"/>
+      <c r="E1229" s="58"/>
+      <c r="F1229" s="58"/>
+      <c r="G1229" s="58"/>
+      <c r="H1229" s="58"/>
+      <c r="I1229" s="58"/>
+      <c r="J1229" s="58"/>
+      <c r="K1229" s="58"/>
+      <c r="L1229" s="58"/>
+      <c r="M1229" s="58"/>
+      <c r="N1229" s="58"/>
+      <c r="O1229" s="58"/>
+      <c r="P1229" s="58"/>
+      <c r="Q1229" s="58"/>
+      <c r="R1229" s="58"/>
+      <c r="S1229" s="58"/>
+      <c r="T1229" s="58"/>
+      <c r="U1229" s="58"/>
+      <c r="V1229" s="58"/>
+      <c r="W1229" s="58"/>
+      <c r="X1229" s="58"/>
+      <c r="Y1229" s="58"/>
+      <c r="Z1229" s="58"/>
+      <c r="AA1229" s="58"/>
+      <c r="AB1229" s="58"/>
+      <c r="AC1229" s="58"/>
+      <c r="AD1229" s="58"/>
+      <c r="AE1229" s="58"/>
+      <c r="AF1229" s="58"/>
     </row>
     <row r="1230" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1231" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -17798,37 +17420,37 @@
       <c r="AF1389" s="34"/>
     </row>
     <row r="1390" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1390" s="61"/>
-      <c r="C1390" s="61"/>
-      <c r="D1390" s="61"/>
-      <c r="E1390" s="61"/>
-      <c r="F1390" s="61"/>
-      <c r="G1390" s="61"/>
-      <c r="H1390" s="61"/>
-      <c r="I1390" s="61"/>
-      <c r="J1390" s="61"/>
-      <c r="K1390" s="61"/>
-      <c r="L1390" s="61"/>
-      <c r="M1390" s="61"/>
-      <c r="N1390" s="61"/>
-      <c r="O1390" s="61"/>
-      <c r="P1390" s="61"/>
-      <c r="Q1390" s="61"/>
-      <c r="R1390" s="61"/>
-      <c r="S1390" s="61"/>
-      <c r="T1390" s="61"/>
-      <c r="U1390" s="61"/>
-      <c r="V1390" s="61"/>
-      <c r="W1390" s="61"/>
-      <c r="X1390" s="61"/>
-      <c r="Y1390" s="61"/>
-      <c r="Z1390" s="61"/>
-      <c r="AA1390" s="61"/>
-      <c r="AB1390" s="61"/>
-      <c r="AC1390" s="61"/>
-      <c r="AD1390" s="61"/>
-      <c r="AE1390" s="61"/>
-      <c r="AF1390" s="61"/>
+      <c r="B1390" s="58"/>
+      <c r="C1390" s="58"/>
+      <c r="D1390" s="58"/>
+      <c r="E1390" s="58"/>
+      <c r="F1390" s="58"/>
+      <c r="G1390" s="58"/>
+      <c r="H1390" s="58"/>
+      <c r="I1390" s="58"/>
+      <c r="J1390" s="58"/>
+      <c r="K1390" s="58"/>
+      <c r="L1390" s="58"/>
+      <c r="M1390" s="58"/>
+      <c r="N1390" s="58"/>
+      <c r="O1390" s="58"/>
+      <c r="P1390" s="58"/>
+      <c r="Q1390" s="58"/>
+      <c r="R1390" s="58"/>
+      <c r="S1390" s="58"/>
+      <c r="T1390" s="58"/>
+      <c r="U1390" s="58"/>
+      <c r="V1390" s="58"/>
+      <c r="W1390" s="58"/>
+      <c r="X1390" s="58"/>
+      <c r="Y1390" s="58"/>
+      <c r="Z1390" s="58"/>
+      <c r="AA1390" s="58"/>
+      <c r="AB1390" s="58"/>
+      <c r="AC1390" s="58"/>
+      <c r="AD1390" s="58"/>
+      <c r="AE1390" s="58"/>
+      <c r="AF1390" s="58"/>
     </row>
     <row r="1391" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1392" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -18021,37 +17643,37 @@
       <c r="AF1501" s="34"/>
     </row>
     <row r="1502" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1502" s="61"/>
-      <c r="C1502" s="61"/>
-      <c r="D1502" s="61"/>
-      <c r="E1502" s="61"/>
-      <c r="F1502" s="61"/>
-      <c r="G1502" s="61"/>
-      <c r="H1502" s="61"/>
-      <c r="I1502" s="61"/>
-      <c r="J1502" s="61"/>
-      <c r="K1502" s="61"/>
-      <c r="L1502" s="61"/>
-      <c r="M1502" s="61"/>
-      <c r="N1502" s="61"/>
-      <c r="O1502" s="61"/>
-      <c r="P1502" s="61"/>
-      <c r="Q1502" s="61"/>
-      <c r="R1502" s="61"/>
-      <c r="S1502" s="61"/>
-      <c r="T1502" s="61"/>
-      <c r="U1502" s="61"/>
-      <c r="V1502" s="61"/>
-      <c r="W1502" s="61"/>
-      <c r="X1502" s="61"/>
-      <c r="Y1502" s="61"/>
-      <c r="Z1502" s="61"/>
-      <c r="AA1502" s="61"/>
-      <c r="AB1502" s="61"/>
-      <c r="AC1502" s="61"/>
-      <c r="AD1502" s="61"/>
-      <c r="AE1502" s="61"/>
-      <c r="AF1502" s="61"/>
+      <c r="B1502" s="58"/>
+      <c r="C1502" s="58"/>
+      <c r="D1502" s="58"/>
+      <c r="E1502" s="58"/>
+      <c r="F1502" s="58"/>
+      <c r="G1502" s="58"/>
+      <c r="H1502" s="58"/>
+      <c r="I1502" s="58"/>
+      <c r="J1502" s="58"/>
+      <c r="K1502" s="58"/>
+      <c r="L1502" s="58"/>
+      <c r="M1502" s="58"/>
+      <c r="N1502" s="58"/>
+      <c r="O1502" s="58"/>
+      <c r="P1502" s="58"/>
+      <c r="Q1502" s="58"/>
+      <c r="R1502" s="58"/>
+      <c r="S1502" s="58"/>
+      <c r="T1502" s="58"/>
+      <c r="U1502" s="58"/>
+      <c r="V1502" s="58"/>
+      <c r="W1502" s="58"/>
+      <c r="X1502" s="58"/>
+      <c r="Y1502" s="58"/>
+      <c r="Z1502" s="58"/>
+      <c r="AA1502" s="58"/>
+      <c r="AB1502" s="58"/>
+      <c r="AC1502" s="58"/>
+      <c r="AD1502" s="58"/>
+      <c r="AE1502" s="58"/>
+      <c r="AF1502" s="58"/>
     </row>
     <row r="1503" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1504" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -18134,37 +17756,37 @@
       <c r="AF1603" s="34"/>
     </row>
     <row r="1604" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1604" s="61"/>
-      <c r="C1604" s="61"/>
-      <c r="D1604" s="61"/>
-      <c r="E1604" s="61"/>
-      <c r="F1604" s="61"/>
-      <c r="G1604" s="61"/>
-      <c r="H1604" s="61"/>
-      <c r="I1604" s="61"/>
-      <c r="J1604" s="61"/>
-      <c r="K1604" s="61"/>
-      <c r="L1604" s="61"/>
-      <c r="M1604" s="61"/>
-      <c r="N1604" s="61"/>
-      <c r="O1604" s="61"/>
-      <c r="P1604" s="61"/>
-      <c r="Q1604" s="61"/>
-      <c r="R1604" s="61"/>
-      <c r="S1604" s="61"/>
-      <c r="T1604" s="61"/>
-      <c r="U1604" s="61"/>
-      <c r="V1604" s="61"/>
-      <c r="W1604" s="61"/>
-      <c r="X1604" s="61"/>
-      <c r="Y1604" s="61"/>
-      <c r="Z1604" s="61"/>
-      <c r="AA1604" s="61"/>
-      <c r="AB1604" s="61"/>
-      <c r="AC1604" s="61"/>
-      <c r="AD1604" s="61"/>
-      <c r="AE1604" s="61"/>
-      <c r="AF1604" s="61"/>
+      <c r="B1604" s="58"/>
+      <c r="C1604" s="58"/>
+      <c r="D1604" s="58"/>
+      <c r="E1604" s="58"/>
+      <c r="F1604" s="58"/>
+      <c r="G1604" s="58"/>
+      <c r="H1604" s="58"/>
+      <c r="I1604" s="58"/>
+      <c r="J1604" s="58"/>
+      <c r="K1604" s="58"/>
+      <c r="L1604" s="58"/>
+      <c r="M1604" s="58"/>
+      <c r="N1604" s="58"/>
+      <c r="O1604" s="58"/>
+      <c r="P1604" s="58"/>
+      <c r="Q1604" s="58"/>
+      <c r="R1604" s="58"/>
+      <c r="S1604" s="58"/>
+      <c r="T1604" s="58"/>
+      <c r="U1604" s="58"/>
+      <c r="V1604" s="58"/>
+      <c r="W1604" s="58"/>
+      <c r="X1604" s="58"/>
+      <c r="Y1604" s="58"/>
+      <c r="Z1604" s="58"/>
+      <c r="AA1604" s="58"/>
+      <c r="AB1604" s="58"/>
+      <c r="AC1604" s="58"/>
+      <c r="AD1604" s="58"/>
+      <c r="AE1604" s="58"/>
+      <c r="AF1604" s="58"/>
     </row>
     <row r="1605" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1606" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -18469,37 +18091,37 @@
       <c r="AF1698" s="34"/>
     </row>
     <row r="1699" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1699" s="61"/>
-      <c r="C1699" s="61"/>
-      <c r="D1699" s="61"/>
-      <c r="E1699" s="61"/>
-      <c r="F1699" s="61"/>
-      <c r="G1699" s="61"/>
-      <c r="H1699" s="61"/>
-      <c r="I1699" s="61"/>
-      <c r="J1699" s="61"/>
-      <c r="K1699" s="61"/>
-      <c r="L1699" s="61"/>
-      <c r="M1699" s="61"/>
-      <c r="N1699" s="61"/>
-      <c r="O1699" s="61"/>
-      <c r="P1699" s="61"/>
-      <c r="Q1699" s="61"/>
-      <c r="R1699" s="61"/>
-      <c r="S1699" s="61"/>
-      <c r="T1699" s="61"/>
-      <c r="U1699" s="61"/>
-      <c r="V1699" s="61"/>
-      <c r="W1699" s="61"/>
-      <c r="X1699" s="61"/>
-      <c r="Y1699" s="61"/>
-      <c r="Z1699" s="61"/>
-      <c r="AA1699" s="61"/>
-      <c r="AB1699" s="61"/>
-      <c r="AC1699" s="61"/>
-      <c r="AD1699" s="61"/>
-      <c r="AE1699" s="61"/>
-      <c r="AF1699" s="61"/>
+      <c r="B1699" s="58"/>
+      <c r="C1699" s="58"/>
+      <c r="D1699" s="58"/>
+      <c r="E1699" s="58"/>
+      <c r="F1699" s="58"/>
+      <c r="G1699" s="58"/>
+      <c r="H1699" s="58"/>
+      <c r="I1699" s="58"/>
+      <c r="J1699" s="58"/>
+      <c r="K1699" s="58"/>
+      <c r="L1699" s="58"/>
+      <c r="M1699" s="58"/>
+      <c r="N1699" s="58"/>
+      <c r="O1699" s="58"/>
+      <c r="P1699" s="58"/>
+      <c r="Q1699" s="58"/>
+      <c r="R1699" s="58"/>
+      <c r="S1699" s="58"/>
+      <c r="T1699" s="58"/>
+      <c r="U1699" s="58"/>
+      <c r="V1699" s="58"/>
+      <c r="W1699" s="58"/>
+      <c r="X1699" s="58"/>
+      <c r="Y1699" s="58"/>
+      <c r="Z1699" s="58"/>
+      <c r="AA1699" s="58"/>
+      <c r="AB1699" s="58"/>
+      <c r="AC1699" s="58"/>
+      <c r="AD1699" s="58"/>
+      <c r="AE1699" s="58"/>
+      <c r="AF1699" s="58"/>
     </row>
     <row r="1700" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1701" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -18641,37 +18263,37 @@
       <c r="AF1944" s="34"/>
     </row>
     <row r="1945" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1945" s="61"/>
-      <c r="C1945" s="61"/>
-      <c r="D1945" s="61"/>
-      <c r="E1945" s="61"/>
-      <c r="F1945" s="61"/>
-      <c r="G1945" s="61"/>
-      <c r="H1945" s="61"/>
-      <c r="I1945" s="61"/>
-      <c r="J1945" s="61"/>
-      <c r="K1945" s="61"/>
-      <c r="L1945" s="61"/>
-      <c r="M1945" s="61"/>
-      <c r="N1945" s="61"/>
-      <c r="O1945" s="61"/>
-      <c r="P1945" s="61"/>
-      <c r="Q1945" s="61"/>
-      <c r="R1945" s="61"/>
-      <c r="S1945" s="61"/>
-      <c r="T1945" s="61"/>
-      <c r="U1945" s="61"/>
-      <c r="V1945" s="61"/>
-      <c r="W1945" s="61"/>
-      <c r="X1945" s="61"/>
-      <c r="Y1945" s="61"/>
-      <c r="Z1945" s="61"/>
-      <c r="AA1945" s="61"/>
-      <c r="AB1945" s="61"/>
-      <c r="AC1945" s="61"/>
-      <c r="AD1945" s="61"/>
-      <c r="AE1945" s="61"/>
-      <c r="AF1945" s="61"/>
+      <c r="B1945" s="58"/>
+      <c r="C1945" s="58"/>
+      <c r="D1945" s="58"/>
+      <c r="E1945" s="58"/>
+      <c r="F1945" s="58"/>
+      <c r="G1945" s="58"/>
+      <c r="H1945" s="58"/>
+      <c r="I1945" s="58"/>
+      <c r="J1945" s="58"/>
+      <c r="K1945" s="58"/>
+      <c r="L1945" s="58"/>
+      <c r="M1945" s="58"/>
+      <c r="N1945" s="58"/>
+      <c r="O1945" s="58"/>
+      <c r="P1945" s="58"/>
+      <c r="Q1945" s="58"/>
+      <c r="R1945" s="58"/>
+      <c r="S1945" s="58"/>
+      <c r="T1945" s="58"/>
+      <c r="U1945" s="58"/>
+      <c r="V1945" s="58"/>
+      <c r="W1945" s="58"/>
+      <c r="X1945" s="58"/>
+      <c r="Y1945" s="58"/>
+      <c r="Z1945" s="58"/>
+      <c r="AA1945" s="58"/>
+      <c r="AB1945" s="58"/>
+      <c r="AC1945" s="58"/>
+      <c r="AD1945" s="58"/>
+      <c r="AE1945" s="58"/>
+      <c r="AF1945" s="58"/>
     </row>
     <row r="1946" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1947" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -18797,37 +18419,37 @@
       <c r="AF2030" s="34"/>
     </row>
     <row r="2031" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2031" s="61"/>
-      <c r="C2031" s="61"/>
-      <c r="D2031" s="61"/>
-      <c r="E2031" s="61"/>
-      <c r="F2031" s="61"/>
-      <c r="G2031" s="61"/>
-      <c r="H2031" s="61"/>
-      <c r="I2031" s="61"/>
-      <c r="J2031" s="61"/>
-      <c r="K2031" s="61"/>
-      <c r="L2031" s="61"/>
-      <c r="M2031" s="61"/>
-      <c r="N2031" s="61"/>
-      <c r="O2031" s="61"/>
-      <c r="P2031" s="61"/>
-      <c r="Q2031" s="61"/>
-      <c r="R2031" s="61"/>
-      <c r="S2031" s="61"/>
-      <c r="T2031" s="61"/>
-      <c r="U2031" s="61"/>
-      <c r="V2031" s="61"/>
-      <c r="W2031" s="61"/>
-      <c r="X2031" s="61"/>
-      <c r="Y2031" s="61"/>
-      <c r="Z2031" s="61"/>
-      <c r="AA2031" s="61"/>
-      <c r="AB2031" s="61"/>
-      <c r="AC2031" s="61"/>
-      <c r="AD2031" s="61"/>
-      <c r="AE2031" s="61"/>
-      <c r="AF2031" s="61"/>
+      <c r="B2031" s="58"/>
+      <c r="C2031" s="58"/>
+      <c r="D2031" s="58"/>
+      <c r="E2031" s="58"/>
+      <c r="F2031" s="58"/>
+      <c r="G2031" s="58"/>
+      <c r="H2031" s="58"/>
+      <c r="I2031" s="58"/>
+      <c r="J2031" s="58"/>
+      <c r="K2031" s="58"/>
+      <c r="L2031" s="58"/>
+      <c r="M2031" s="58"/>
+      <c r="N2031" s="58"/>
+      <c r="O2031" s="58"/>
+      <c r="P2031" s="58"/>
+      <c r="Q2031" s="58"/>
+      <c r="R2031" s="58"/>
+      <c r="S2031" s="58"/>
+      <c r="T2031" s="58"/>
+      <c r="U2031" s="58"/>
+      <c r="V2031" s="58"/>
+      <c r="W2031" s="58"/>
+      <c r="X2031" s="58"/>
+      <c r="Y2031" s="58"/>
+      <c r="Z2031" s="58"/>
+      <c r="AA2031" s="58"/>
+      <c r="AB2031" s="58"/>
+      <c r="AC2031" s="58"/>
+      <c r="AD2031" s="58"/>
+      <c r="AE2031" s="58"/>
+      <c r="AF2031" s="58"/>
     </row>
     <row r="2032" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2033" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19027,37 +18649,37 @@
       <c r="AF2152" s="34"/>
     </row>
     <row r="2153" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2153" s="61"/>
-      <c r="C2153" s="61"/>
-      <c r="D2153" s="61"/>
-      <c r="E2153" s="61"/>
-      <c r="F2153" s="61"/>
-      <c r="G2153" s="61"/>
-      <c r="H2153" s="61"/>
-      <c r="I2153" s="61"/>
-      <c r="J2153" s="61"/>
-      <c r="K2153" s="61"/>
-      <c r="L2153" s="61"/>
-      <c r="M2153" s="61"/>
-      <c r="N2153" s="61"/>
-      <c r="O2153" s="61"/>
-      <c r="P2153" s="61"/>
-      <c r="Q2153" s="61"/>
-      <c r="R2153" s="61"/>
-      <c r="S2153" s="61"/>
-      <c r="T2153" s="61"/>
-      <c r="U2153" s="61"/>
-      <c r="V2153" s="61"/>
-      <c r="W2153" s="61"/>
-      <c r="X2153" s="61"/>
-      <c r="Y2153" s="61"/>
-      <c r="Z2153" s="61"/>
-      <c r="AA2153" s="61"/>
-      <c r="AB2153" s="61"/>
-      <c r="AC2153" s="61"/>
-      <c r="AD2153" s="61"/>
-      <c r="AE2153" s="61"/>
-      <c r="AF2153" s="61"/>
+      <c r="B2153" s="58"/>
+      <c r="C2153" s="58"/>
+      <c r="D2153" s="58"/>
+      <c r="E2153" s="58"/>
+      <c r="F2153" s="58"/>
+      <c r="G2153" s="58"/>
+      <c r="H2153" s="58"/>
+      <c r="I2153" s="58"/>
+      <c r="J2153" s="58"/>
+      <c r="K2153" s="58"/>
+      <c r="L2153" s="58"/>
+      <c r="M2153" s="58"/>
+      <c r="N2153" s="58"/>
+      <c r="O2153" s="58"/>
+      <c r="P2153" s="58"/>
+      <c r="Q2153" s="58"/>
+      <c r="R2153" s="58"/>
+      <c r="S2153" s="58"/>
+      <c r="T2153" s="58"/>
+      <c r="U2153" s="58"/>
+      <c r="V2153" s="58"/>
+      <c r="W2153" s="58"/>
+      <c r="X2153" s="58"/>
+      <c r="Y2153" s="58"/>
+      <c r="Z2153" s="58"/>
+      <c r="AA2153" s="58"/>
+      <c r="AB2153" s="58"/>
+      <c r="AC2153" s="58"/>
+      <c r="AD2153" s="58"/>
+      <c r="AE2153" s="58"/>
+      <c r="AF2153" s="58"/>
     </row>
     <row r="2154" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2155" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19157,37 +18779,37 @@
       <c r="AF2316" s="34"/>
     </row>
     <row r="2317" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2317" s="61"/>
-      <c r="C2317" s="61"/>
-      <c r="D2317" s="61"/>
-      <c r="E2317" s="61"/>
-      <c r="F2317" s="61"/>
-      <c r="G2317" s="61"/>
-      <c r="H2317" s="61"/>
-      <c r="I2317" s="61"/>
-      <c r="J2317" s="61"/>
-      <c r="K2317" s="61"/>
-      <c r="L2317" s="61"/>
-      <c r="M2317" s="61"/>
-      <c r="N2317" s="61"/>
-      <c r="O2317" s="61"/>
-      <c r="P2317" s="61"/>
-      <c r="Q2317" s="61"/>
-      <c r="R2317" s="61"/>
-      <c r="S2317" s="61"/>
-      <c r="T2317" s="61"/>
-      <c r="U2317" s="61"/>
-      <c r="V2317" s="61"/>
-      <c r="W2317" s="61"/>
-      <c r="X2317" s="61"/>
-      <c r="Y2317" s="61"/>
-      <c r="Z2317" s="61"/>
-      <c r="AA2317" s="61"/>
-      <c r="AB2317" s="61"/>
-      <c r="AC2317" s="61"/>
-      <c r="AD2317" s="61"/>
-      <c r="AE2317" s="61"/>
-      <c r="AF2317" s="61"/>
+      <c r="B2317" s="58"/>
+      <c r="C2317" s="58"/>
+      <c r="D2317" s="58"/>
+      <c r="E2317" s="58"/>
+      <c r="F2317" s="58"/>
+      <c r="G2317" s="58"/>
+      <c r="H2317" s="58"/>
+      <c r="I2317" s="58"/>
+      <c r="J2317" s="58"/>
+      <c r="K2317" s="58"/>
+      <c r="L2317" s="58"/>
+      <c r="M2317" s="58"/>
+      <c r="N2317" s="58"/>
+      <c r="O2317" s="58"/>
+      <c r="P2317" s="58"/>
+      <c r="Q2317" s="58"/>
+      <c r="R2317" s="58"/>
+      <c r="S2317" s="58"/>
+      <c r="T2317" s="58"/>
+      <c r="U2317" s="58"/>
+      <c r="V2317" s="58"/>
+      <c r="W2317" s="58"/>
+      <c r="X2317" s="58"/>
+      <c r="Y2317" s="58"/>
+      <c r="Z2317" s="58"/>
+      <c r="AA2317" s="58"/>
+      <c r="AB2317" s="58"/>
+      <c r="AC2317" s="58"/>
+      <c r="AD2317" s="58"/>
+      <c r="AE2317" s="58"/>
+      <c r="AF2317" s="58"/>
     </row>
     <row r="2318" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2319" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19302,37 +18924,37 @@
       <c r="AF2418" s="34"/>
     </row>
     <row r="2419" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2419" s="61"/>
-      <c r="C2419" s="61"/>
-      <c r="D2419" s="61"/>
-      <c r="E2419" s="61"/>
-      <c r="F2419" s="61"/>
-      <c r="G2419" s="61"/>
-      <c r="H2419" s="61"/>
-      <c r="I2419" s="61"/>
-      <c r="J2419" s="61"/>
-      <c r="K2419" s="61"/>
-      <c r="L2419" s="61"/>
-      <c r="M2419" s="61"/>
-      <c r="N2419" s="61"/>
-      <c r="O2419" s="61"/>
-      <c r="P2419" s="61"/>
-      <c r="Q2419" s="61"/>
-      <c r="R2419" s="61"/>
-      <c r="S2419" s="61"/>
-      <c r="T2419" s="61"/>
-      <c r="U2419" s="61"/>
-      <c r="V2419" s="61"/>
-      <c r="W2419" s="61"/>
-      <c r="X2419" s="61"/>
-      <c r="Y2419" s="61"/>
-      <c r="Z2419" s="61"/>
-      <c r="AA2419" s="61"/>
-      <c r="AB2419" s="61"/>
-      <c r="AC2419" s="61"/>
-      <c r="AD2419" s="61"/>
-      <c r="AE2419" s="61"/>
-      <c r="AF2419" s="61"/>
+      <c r="B2419" s="58"/>
+      <c r="C2419" s="58"/>
+      <c r="D2419" s="58"/>
+      <c r="E2419" s="58"/>
+      <c r="F2419" s="58"/>
+      <c r="G2419" s="58"/>
+      <c r="H2419" s="58"/>
+      <c r="I2419" s="58"/>
+      <c r="J2419" s="58"/>
+      <c r="K2419" s="58"/>
+      <c r="L2419" s="58"/>
+      <c r="M2419" s="58"/>
+      <c r="N2419" s="58"/>
+      <c r="O2419" s="58"/>
+      <c r="P2419" s="58"/>
+      <c r="Q2419" s="58"/>
+      <c r="R2419" s="58"/>
+      <c r="S2419" s="58"/>
+      <c r="T2419" s="58"/>
+      <c r="U2419" s="58"/>
+      <c r="V2419" s="58"/>
+      <c r="W2419" s="58"/>
+      <c r="X2419" s="58"/>
+      <c r="Y2419" s="58"/>
+      <c r="Z2419" s="58"/>
+      <c r="AA2419" s="58"/>
+      <c r="AB2419" s="58"/>
+      <c r="AC2419" s="58"/>
+      <c r="AD2419" s="58"/>
+      <c r="AE2419" s="58"/>
+      <c r="AF2419" s="58"/>
     </row>
     <row r="2420" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2421" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19499,37 +19121,37 @@
       <c r="AF2508" s="34"/>
     </row>
     <row r="2509" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2509" s="61"/>
-      <c r="C2509" s="61"/>
-      <c r="D2509" s="61"/>
-      <c r="E2509" s="61"/>
-      <c r="F2509" s="61"/>
-      <c r="G2509" s="61"/>
-      <c r="H2509" s="61"/>
-      <c r="I2509" s="61"/>
-      <c r="J2509" s="61"/>
-      <c r="K2509" s="61"/>
-      <c r="L2509" s="61"/>
-      <c r="M2509" s="61"/>
-      <c r="N2509" s="61"/>
-      <c r="O2509" s="61"/>
-      <c r="P2509" s="61"/>
-      <c r="Q2509" s="61"/>
-      <c r="R2509" s="61"/>
-      <c r="S2509" s="61"/>
-      <c r="T2509" s="61"/>
-      <c r="U2509" s="61"/>
-      <c r="V2509" s="61"/>
-      <c r="W2509" s="61"/>
-      <c r="X2509" s="61"/>
-      <c r="Y2509" s="61"/>
-      <c r="Z2509" s="61"/>
-      <c r="AA2509" s="61"/>
-      <c r="AB2509" s="61"/>
-      <c r="AC2509" s="61"/>
-      <c r="AD2509" s="61"/>
-      <c r="AE2509" s="61"/>
-      <c r="AF2509" s="61"/>
+      <c r="B2509" s="58"/>
+      <c r="C2509" s="58"/>
+      <c r="D2509" s="58"/>
+      <c r="E2509" s="58"/>
+      <c r="F2509" s="58"/>
+      <c r="G2509" s="58"/>
+      <c r="H2509" s="58"/>
+      <c r="I2509" s="58"/>
+      <c r="J2509" s="58"/>
+      <c r="K2509" s="58"/>
+      <c r="L2509" s="58"/>
+      <c r="M2509" s="58"/>
+      <c r="N2509" s="58"/>
+      <c r="O2509" s="58"/>
+      <c r="P2509" s="58"/>
+      <c r="Q2509" s="58"/>
+      <c r="R2509" s="58"/>
+      <c r="S2509" s="58"/>
+      <c r="T2509" s="58"/>
+      <c r="U2509" s="58"/>
+      <c r="V2509" s="58"/>
+      <c r="W2509" s="58"/>
+      <c r="X2509" s="58"/>
+      <c r="Y2509" s="58"/>
+      <c r="Z2509" s="58"/>
+      <c r="AA2509" s="58"/>
+      <c r="AB2509" s="58"/>
+      <c r="AC2509" s="58"/>
+      <c r="AD2509" s="58"/>
+      <c r="AE2509" s="58"/>
+      <c r="AF2509" s="58"/>
     </row>
     <row r="2510" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2511" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19659,37 +19281,37 @@
       <c r="AF2597" s="34"/>
     </row>
     <row r="2598" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2598" s="61"/>
-      <c r="C2598" s="61"/>
-      <c r="D2598" s="61"/>
-      <c r="E2598" s="61"/>
-      <c r="F2598" s="61"/>
-      <c r="G2598" s="61"/>
-      <c r="H2598" s="61"/>
-      <c r="I2598" s="61"/>
-      <c r="J2598" s="61"/>
-      <c r="K2598" s="61"/>
-      <c r="L2598" s="61"/>
-      <c r="M2598" s="61"/>
-      <c r="N2598" s="61"/>
-      <c r="O2598" s="61"/>
-      <c r="P2598" s="61"/>
-      <c r="Q2598" s="61"/>
-      <c r="R2598" s="61"/>
-      <c r="S2598" s="61"/>
-      <c r="T2598" s="61"/>
-      <c r="U2598" s="61"/>
-      <c r="V2598" s="61"/>
-      <c r="W2598" s="61"/>
-      <c r="X2598" s="61"/>
-      <c r="Y2598" s="61"/>
-      <c r="Z2598" s="61"/>
-      <c r="AA2598" s="61"/>
-      <c r="AB2598" s="61"/>
-      <c r="AC2598" s="61"/>
-      <c r="AD2598" s="61"/>
-      <c r="AE2598" s="61"/>
-      <c r="AF2598" s="61"/>
+      <c r="B2598" s="58"/>
+      <c r="C2598" s="58"/>
+      <c r="D2598" s="58"/>
+      <c r="E2598" s="58"/>
+      <c r="F2598" s="58"/>
+      <c r="G2598" s="58"/>
+      <c r="H2598" s="58"/>
+      <c r="I2598" s="58"/>
+      <c r="J2598" s="58"/>
+      <c r="K2598" s="58"/>
+      <c r="L2598" s="58"/>
+      <c r="M2598" s="58"/>
+      <c r="N2598" s="58"/>
+      <c r="O2598" s="58"/>
+      <c r="P2598" s="58"/>
+      <c r="Q2598" s="58"/>
+      <c r="R2598" s="58"/>
+      <c r="S2598" s="58"/>
+      <c r="T2598" s="58"/>
+      <c r="U2598" s="58"/>
+      <c r="V2598" s="58"/>
+      <c r="W2598" s="58"/>
+      <c r="X2598" s="58"/>
+      <c r="Y2598" s="58"/>
+      <c r="Z2598" s="58"/>
+      <c r="AA2598" s="58"/>
+      <c r="AB2598" s="58"/>
+      <c r="AC2598" s="58"/>
+      <c r="AD2598" s="58"/>
+      <c r="AE2598" s="58"/>
+      <c r="AF2598" s="58"/>
     </row>
     <row r="2599" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2600" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19895,37 +19517,37 @@
       <c r="AF2718" s="34"/>
     </row>
     <row r="2719" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2719" s="61"/>
-      <c r="C2719" s="61"/>
-      <c r="D2719" s="61"/>
-      <c r="E2719" s="61"/>
-      <c r="F2719" s="61"/>
-      <c r="G2719" s="61"/>
-      <c r="H2719" s="61"/>
-      <c r="I2719" s="61"/>
-      <c r="J2719" s="61"/>
-      <c r="K2719" s="61"/>
-      <c r="L2719" s="61"/>
-      <c r="M2719" s="61"/>
-      <c r="N2719" s="61"/>
-      <c r="O2719" s="61"/>
-      <c r="P2719" s="61"/>
-      <c r="Q2719" s="61"/>
-      <c r="R2719" s="61"/>
-      <c r="S2719" s="61"/>
-      <c r="T2719" s="61"/>
-      <c r="U2719" s="61"/>
-      <c r="V2719" s="61"/>
-      <c r="W2719" s="61"/>
-      <c r="X2719" s="61"/>
-      <c r="Y2719" s="61"/>
-      <c r="Z2719" s="61"/>
-      <c r="AA2719" s="61"/>
-      <c r="AB2719" s="61"/>
-      <c r="AC2719" s="61"/>
-      <c r="AD2719" s="61"/>
-      <c r="AE2719" s="61"/>
-      <c r="AF2719" s="61"/>
+      <c r="B2719" s="58"/>
+      <c r="C2719" s="58"/>
+      <c r="D2719" s="58"/>
+      <c r="E2719" s="58"/>
+      <c r="F2719" s="58"/>
+      <c r="G2719" s="58"/>
+      <c r="H2719" s="58"/>
+      <c r="I2719" s="58"/>
+      <c r="J2719" s="58"/>
+      <c r="K2719" s="58"/>
+      <c r="L2719" s="58"/>
+      <c r="M2719" s="58"/>
+      <c r="N2719" s="58"/>
+      <c r="O2719" s="58"/>
+      <c r="P2719" s="58"/>
+      <c r="Q2719" s="58"/>
+      <c r="R2719" s="58"/>
+      <c r="S2719" s="58"/>
+      <c r="T2719" s="58"/>
+      <c r="U2719" s="58"/>
+      <c r="V2719" s="58"/>
+      <c r="W2719" s="58"/>
+      <c r="X2719" s="58"/>
+      <c r="Y2719" s="58"/>
+      <c r="Z2719" s="58"/>
+      <c r="AA2719" s="58"/>
+      <c r="AB2719" s="58"/>
+      <c r="AC2719" s="58"/>
+      <c r="AD2719" s="58"/>
+      <c r="AE2719" s="58"/>
+      <c r="AF2719" s="58"/>
     </row>
     <row r="2720" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2721" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -20038,37 +19660,37 @@
       <c r="AF2836" s="34"/>
     </row>
     <row r="2837" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2837" s="61"/>
-      <c r="C2837" s="61"/>
-      <c r="D2837" s="61"/>
-      <c r="E2837" s="61"/>
-      <c r="F2837" s="61"/>
-      <c r="G2837" s="61"/>
-      <c r="H2837" s="61"/>
-      <c r="I2837" s="61"/>
-      <c r="J2837" s="61"/>
-      <c r="K2837" s="61"/>
-      <c r="L2837" s="61"/>
-      <c r="M2837" s="61"/>
-      <c r="N2837" s="61"/>
-      <c r="O2837" s="61"/>
-      <c r="P2837" s="61"/>
-      <c r="Q2837" s="61"/>
-      <c r="R2837" s="61"/>
-      <c r="S2837" s="61"/>
-      <c r="T2837" s="61"/>
-      <c r="U2837" s="61"/>
-      <c r="V2837" s="61"/>
-      <c r="W2837" s="61"/>
-      <c r="X2837" s="61"/>
-      <c r="Y2837" s="61"/>
-      <c r="Z2837" s="61"/>
-      <c r="AA2837" s="61"/>
-      <c r="AB2837" s="61"/>
-      <c r="AC2837" s="61"/>
-      <c r="AD2837" s="61"/>
-      <c r="AE2837" s="61"/>
-      <c r="AF2837" s="61"/>
+      <c r="B2837" s="58"/>
+      <c r="C2837" s="58"/>
+      <c r="D2837" s="58"/>
+      <c r="E2837" s="58"/>
+      <c r="F2837" s="58"/>
+      <c r="G2837" s="58"/>
+      <c r="H2837" s="58"/>
+      <c r="I2837" s="58"/>
+      <c r="J2837" s="58"/>
+      <c r="K2837" s="58"/>
+      <c r="L2837" s="58"/>
+      <c r="M2837" s="58"/>
+      <c r="N2837" s="58"/>
+      <c r="O2837" s="58"/>
+      <c r="P2837" s="58"/>
+      <c r="Q2837" s="58"/>
+      <c r="R2837" s="58"/>
+      <c r="S2837" s="58"/>
+      <c r="T2837" s="58"/>
+      <c r="U2837" s="58"/>
+      <c r="V2837" s="58"/>
+      <c r="W2837" s="58"/>
+      <c r="X2837" s="58"/>
+      <c r="Y2837" s="58"/>
+      <c r="Z2837" s="58"/>
+      <c r="AA2837" s="58"/>
+      <c r="AB2837" s="58"/>
+      <c r="AC2837" s="58"/>
+      <c r="AD2837" s="58"/>
+      <c r="AE2837" s="58"/>
+      <c r="AF2837" s="58"/>
     </row>
     <row r="2838" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2839" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -20076,14 +19698,6 @@
     <row r="2841" spans="2:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2719:AF2719"/>
-    <mergeCell ref="B2837:AF2837"/>
-    <mergeCell ref="B2031:AF2031"/>
-    <mergeCell ref="B2153:AF2153"/>
-    <mergeCell ref="B2317:AF2317"/>
-    <mergeCell ref="B2419:AF2419"/>
-    <mergeCell ref="B2509:AF2509"/>
-    <mergeCell ref="B2598:AF2598"/>
     <mergeCell ref="B146:AG146"/>
     <mergeCell ref="B1945:AF1945"/>
     <mergeCell ref="B308:AF308"/>
@@ -20096,6 +19710,14 @@
     <mergeCell ref="B1502:AF1502"/>
     <mergeCell ref="B1604:AF1604"/>
     <mergeCell ref="B1699:AF1699"/>
+    <mergeCell ref="B2719:AF2719"/>
+    <mergeCell ref="B2837:AF2837"/>
+    <mergeCell ref="B2031:AF2031"/>
+    <mergeCell ref="B2153:AF2153"/>
+    <mergeCell ref="B2317:AF2317"/>
+    <mergeCell ref="B2419:AF2419"/>
+    <mergeCell ref="B2509:AF2509"/>
+    <mergeCell ref="B2598:AF2598"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30414,38 +30036,38 @@
     <row r="306" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="307" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="308" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B308" s="62"/>
-      <c r="C308" s="62"/>
-      <c r="D308" s="62"/>
-      <c r="E308" s="62"/>
-      <c r="F308" s="62"/>
-      <c r="G308" s="62"/>
-      <c r="H308" s="62"/>
-      <c r="I308" s="62"/>
-      <c r="J308" s="62"/>
-      <c r="K308" s="62"/>
-      <c r="L308" s="62"/>
-      <c r="M308" s="62"/>
-      <c r="N308" s="62"/>
-      <c r="O308" s="62"/>
-      <c r="P308" s="62"/>
-      <c r="Q308" s="62"/>
-      <c r="R308" s="62"/>
-      <c r="S308" s="62"/>
-      <c r="T308" s="62"/>
-      <c r="U308" s="62"/>
-      <c r="V308" s="62"/>
-      <c r="W308" s="62"/>
-      <c r="X308" s="62"/>
-      <c r="Y308" s="62"/>
-      <c r="Z308" s="62"/>
-      <c r="AA308" s="62"/>
-      <c r="AB308" s="62"/>
-      <c r="AC308" s="62"/>
-      <c r="AD308" s="62"/>
-      <c r="AE308" s="62"/>
-      <c r="AF308" s="62"/>
-      <c r="AG308" s="62"/>
+      <c r="B308" s="61"/>
+      <c r="C308" s="61"/>
+      <c r="D308" s="61"/>
+      <c r="E308" s="61"/>
+      <c r="F308" s="61"/>
+      <c r="G308" s="61"/>
+      <c r="H308" s="61"/>
+      <c r="I308" s="61"/>
+      <c r="J308" s="61"/>
+      <c r="K308" s="61"/>
+      <c r="L308" s="61"/>
+      <c r="M308" s="61"/>
+      <c r="N308" s="61"/>
+      <c r="O308" s="61"/>
+      <c r="P308" s="61"/>
+      <c r="Q308" s="61"/>
+      <c r="R308" s="61"/>
+      <c r="S308" s="61"/>
+      <c r="T308" s="61"/>
+      <c r="U308" s="61"/>
+      <c r="V308" s="61"/>
+      <c r="W308" s="61"/>
+      <c r="X308" s="61"/>
+      <c r="Y308" s="61"/>
+      <c r="Z308" s="61"/>
+      <c r="AA308" s="61"/>
+      <c r="AB308" s="61"/>
+      <c r="AC308" s="61"/>
+      <c r="AD308" s="61"/>
+      <c r="AE308" s="61"/>
+      <c r="AF308" s="61"/>
+      <c r="AG308" s="61"/>
     </row>
     <row r="309" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="310" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -30604,38 +30226,38 @@
     <row r="508" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="510" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="511" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B511" s="62"/>
-      <c r="C511" s="62"/>
-      <c r="D511" s="62"/>
-      <c r="E511" s="62"/>
-      <c r="F511" s="62"/>
-      <c r="G511" s="62"/>
-      <c r="H511" s="62"/>
-      <c r="I511" s="62"/>
-      <c r="J511" s="62"/>
-      <c r="K511" s="62"/>
-      <c r="L511" s="62"/>
-      <c r="M511" s="62"/>
-      <c r="N511" s="62"/>
-      <c r="O511" s="62"/>
-      <c r="P511" s="62"/>
-      <c r="Q511" s="62"/>
-      <c r="R511" s="62"/>
-      <c r="S511" s="62"/>
-      <c r="T511" s="62"/>
-      <c r="U511" s="62"/>
-      <c r="V511" s="62"/>
-      <c r="W511" s="62"/>
-      <c r="X511" s="62"/>
-      <c r="Y511" s="62"/>
-      <c r="Z511" s="62"/>
-      <c r="AA511" s="62"/>
-      <c r="AB511" s="62"/>
-      <c r="AC511" s="62"/>
-      <c r="AD511" s="62"/>
-      <c r="AE511" s="62"/>
-      <c r="AF511" s="62"/>
-      <c r="AG511" s="62"/>
+      <c r="B511" s="61"/>
+      <c r="C511" s="61"/>
+      <c r="D511" s="61"/>
+      <c r="E511" s="61"/>
+      <c r="F511" s="61"/>
+      <c r="G511" s="61"/>
+      <c r="H511" s="61"/>
+      <c r="I511" s="61"/>
+      <c r="J511" s="61"/>
+      <c r="K511" s="61"/>
+      <c r="L511" s="61"/>
+      <c r="M511" s="61"/>
+      <c r="N511" s="61"/>
+      <c r="O511" s="61"/>
+      <c r="P511" s="61"/>
+      <c r="Q511" s="61"/>
+      <c r="R511" s="61"/>
+      <c r="S511" s="61"/>
+      <c r="T511" s="61"/>
+      <c r="U511" s="61"/>
+      <c r="V511" s="61"/>
+      <c r="W511" s="61"/>
+      <c r="X511" s="61"/>
+      <c r="Y511" s="61"/>
+      <c r="Z511" s="61"/>
+      <c r="AA511" s="61"/>
+      <c r="AB511" s="61"/>
+      <c r="AC511" s="61"/>
+      <c r="AD511" s="61"/>
+      <c r="AE511" s="61"/>
+      <c r="AF511" s="61"/>
+      <c r="AG511" s="61"/>
     </row>
     <row r="512" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="513" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -30776,38 +30398,38 @@
     <row r="710" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="711" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="712" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B712" s="62"/>
-      <c r="C712" s="62"/>
-      <c r="D712" s="62"/>
-      <c r="E712" s="62"/>
-      <c r="F712" s="62"/>
-      <c r="G712" s="62"/>
-      <c r="H712" s="62"/>
-      <c r="I712" s="62"/>
-      <c r="J712" s="62"/>
-      <c r="K712" s="62"/>
-      <c r="L712" s="62"/>
-      <c r="M712" s="62"/>
-      <c r="N712" s="62"/>
-      <c r="O712" s="62"/>
-      <c r="P712" s="62"/>
-      <c r="Q712" s="62"/>
-      <c r="R712" s="62"/>
-      <c r="S712" s="62"/>
-      <c r="T712" s="62"/>
-      <c r="U712" s="62"/>
-      <c r="V712" s="62"/>
-      <c r="W712" s="62"/>
-      <c r="X712" s="62"/>
-      <c r="Y712" s="62"/>
-      <c r="Z712" s="62"/>
-      <c r="AA712" s="62"/>
-      <c r="AB712" s="62"/>
-      <c r="AC712" s="62"/>
-      <c r="AD712" s="62"/>
-      <c r="AE712" s="62"/>
-      <c r="AF712" s="62"/>
-      <c r="AG712" s="62"/>
+      <c r="B712" s="61"/>
+      <c r="C712" s="61"/>
+      <c r="D712" s="61"/>
+      <c r="E712" s="61"/>
+      <c r="F712" s="61"/>
+      <c r="G712" s="61"/>
+      <c r="H712" s="61"/>
+      <c r="I712" s="61"/>
+      <c r="J712" s="61"/>
+      <c r="K712" s="61"/>
+      <c r="L712" s="61"/>
+      <c r="M712" s="61"/>
+      <c r="N712" s="61"/>
+      <c r="O712" s="61"/>
+      <c r="P712" s="61"/>
+      <c r="Q712" s="61"/>
+      <c r="R712" s="61"/>
+      <c r="S712" s="61"/>
+      <c r="T712" s="61"/>
+      <c r="U712" s="61"/>
+      <c r="V712" s="61"/>
+      <c r="W712" s="61"/>
+      <c r="X712" s="61"/>
+      <c r="Y712" s="61"/>
+      <c r="Z712" s="61"/>
+      <c r="AA712" s="61"/>
+      <c r="AB712" s="61"/>
+      <c r="AC712" s="61"/>
+      <c r="AD712" s="61"/>
+      <c r="AE712" s="61"/>
+      <c r="AF712" s="61"/>
+      <c r="AG712" s="61"/>
     </row>
     <row r="713" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="714" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -30930,38 +30552,38 @@
     <row r="885" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="886" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="887" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B887" s="62"/>
-      <c r="C887" s="62"/>
-      <c r="D887" s="62"/>
-      <c r="E887" s="62"/>
-      <c r="F887" s="62"/>
-      <c r="G887" s="62"/>
-      <c r="H887" s="62"/>
-      <c r="I887" s="62"/>
-      <c r="J887" s="62"/>
-      <c r="K887" s="62"/>
-      <c r="L887" s="62"/>
-      <c r="M887" s="62"/>
-      <c r="N887" s="62"/>
-      <c r="O887" s="62"/>
-      <c r="P887" s="62"/>
-      <c r="Q887" s="62"/>
-      <c r="R887" s="62"/>
-      <c r="S887" s="62"/>
-      <c r="T887" s="62"/>
-      <c r="U887" s="62"/>
-      <c r="V887" s="62"/>
-      <c r="W887" s="62"/>
-      <c r="X887" s="62"/>
-      <c r="Y887" s="62"/>
-      <c r="Z887" s="62"/>
-      <c r="AA887" s="62"/>
-      <c r="AB887" s="62"/>
-      <c r="AC887" s="62"/>
-      <c r="AD887" s="62"/>
-      <c r="AE887" s="62"/>
-      <c r="AF887" s="62"/>
-      <c r="AG887" s="62"/>
+      <c r="B887" s="61"/>
+      <c r="C887" s="61"/>
+      <c r="D887" s="61"/>
+      <c r="E887" s="61"/>
+      <c r="F887" s="61"/>
+      <c r="G887" s="61"/>
+      <c r="H887" s="61"/>
+      <c r="I887" s="61"/>
+      <c r="J887" s="61"/>
+      <c r="K887" s="61"/>
+      <c r="L887" s="61"/>
+      <c r="M887" s="61"/>
+      <c r="N887" s="61"/>
+      <c r="O887" s="61"/>
+      <c r="P887" s="61"/>
+      <c r="Q887" s="61"/>
+      <c r="R887" s="61"/>
+      <c r="S887" s="61"/>
+      <c r="T887" s="61"/>
+      <c r="U887" s="61"/>
+      <c r="V887" s="61"/>
+      <c r="W887" s="61"/>
+      <c r="X887" s="61"/>
+      <c r="Y887" s="61"/>
+      <c r="Z887" s="61"/>
+      <c r="AA887" s="61"/>
+      <c r="AB887" s="61"/>
+      <c r="AC887" s="61"/>
+      <c r="AD887" s="61"/>
+      <c r="AE887" s="61"/>
+      <c r="AF887" s="61"/>
+      <c r="AG887" s="61"/>
     </row>
     <row r="888" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="889" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31124,38 +30746,38 @@
     <row r="1098" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1099" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1100" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1100" s="62"/>
-      <c r="C1100" s="62"/>
-      <c r="D1100" s="62"/>
-      <c r="E1100" s="62"/>
-      <c r="F1100" s="62"/>
-      <c r="G1100" s="62"/>
-      <c r="H1100" s="62"/>
-      <c r="I1100" s="62"/>
-      <c r="J1100" s="62"/>
-      <c r="K1100" s="62"/>
-      <c r="L1100" s="62"/>
-      <c r="M1100" s="62"/>
-      <c r="N1100" s="62"/>
-      <c r="O1100" s="62"/>
-      <c r="P1100" s="62"/>
-      <c r="Q1100" s="62"/>
-      <c r="R1100" s="62"/>
-      <c r="S1100" s="62"/>
-      <c r="T1100" s="62"/>
-      <c r="U1100" s="62"/>
-      <c r="V1100" s="62"/>
-      <c r="W1100" s="62"/>
-      <c r="X1100" s="62"/>
-      <c r="Y1100" s="62"/>
-      <c r="Z1100" s="62"/>
-      <c r="AA1100" s="62"/>
-      <c r="AB1100" s="62"/>
-      <c r="AC1100" s="62"/>
-      <c r="AD1100" s="62"/>
-      <c r="AE1100" s="62"/>
-      <c r="AF1100" s="62"/>
-      <c r="AG1100" s="62"/>
+      <c r="B1100" s="61"/>
+      <c r="C1100" s="61"/>
+      <c r="D1100" s="61"/>
+      <c r="E1100" s="61"/>
+      <c r="F1100" s="61"/>
+      <c r="G1100" s="61"/>
+      <c r="H1100" s="61"/>
+      <c r="I1100" s="61"/>
+      <c r="J1100" s="61"/>
+      <c r="K1100" s="61"/>
+      <c r="L1100" s="61"/>
+      <c r="M1100" s="61"/>
+      <c r="N1100" s="61"/>
+      <c r="O1100" s="61"/>
+      <c r="P1100" s="61"/>
+      <c r="Q1100" s="61"/>
+      <c r="R1100" s="61"/>
+      <c r="S1100" s="61"/>
+      <c r="T1100" s="61"/>
+      <c r="U1100" s="61"/>
+      <c r="V1100" s="61"/>
+      <c r="W1100" s="61"/>
+      <c r="X1100" s="61"/>
+      <c r="Y1100" s="61"/>
+      <c r="Z1100" s="61"/>
+      <c r="AA1100" s="61"/>
+      <c r="AB1100" s="61"/>
+      <c r="AC1100" s="61"/>
+      <c r="AD1100" s="61"/>
+      <c r="AE1100" s="61"/>
+      <c r="AF1100" s="61"/>
+      <c r="AG1100" s="61"/>
     </row>
     <row r="1101" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1102" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31243,38 +30865,38 @@
     <row r="1225" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1226" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1227" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1227" s="62"/>
-      <c r="C1227" s="62"/>
-      <c r="D1227" s="62"/>
-      <c r="E1227" s="62"/>
-      <c r="F1227" s="62"/>
-      <c r="G1227" s="62"/>
-      <c r="H1227" s="62"/>
-      <c r="I1227" s="62"/>
-      <c r="J1227" s="62"/>
-      <c r="K1227" s="62"/>
-      <c r="L1227" s="62"/>
-      <c r="M1227" s="62"/>
-      <c r="N1227" s="62"/>
-      <c r="O1227" s="62"/>
-      <c r="P1227" s="62"/>
-      <c r="Q1227" s="62"/>
-      <c r="R1227" s="62"/>
-      <c r="S1227" s="62"/>
-      <c r="T1227" s="62"/>
-      <c r="U1227" s="62"/>
-      <c r="V1227" s="62"/>
-      <c r="W1227" s="62"/>
-      <c r="X1227" s="62"/>
-      <c r="Y1227" s="62"/>
-      <c r="Z1227" s="62"/>
-      <c r="AA1227" s="62"/>
-      <c r="AB1227" s="62"/>
-      <c r="AC1227" s="62"/>
-      <c r="AD1227" s="62"/>
-      <c r="AE1227" s="62"/>
-      <c r="AF1227" s="62"/>
-      <c r="AG1227" s="62"/>
+      <c r="B1227" s="61"/>
+      <c r="C1227" s="61"/>
+      <c r="D1227" s="61"/>
+      <c r="E1227" s="61"/>
+      <c r="F1227" s="61"/>
+      <c r="G1227" s="61"/>
+      <c r="H1227" s="61"/>
+      <c r="I1227" s="61"/>
+      <c r="J1227" s="61"/>
+      <c r="K1227" s="61"/>
+      <c r="L1227" s="61"/>
+      <c r="M1227" s="61"/>
+      <c r="N1227" s="61"/>
+      <c r="O1227" s="61"/>
+      <c r="P1227" s="61"/>
+      <c r="Q1227" s="61"/>
+      <c r="R1227" s="61"/>
+      <c r="S1227" s="61"/>
+      <c r="T1227" s="61"/>
+      <c r="U1227" s="61"/>
+      <c r="V1227" s="61"/>
+      <c r="W1227" s="61"/>
+      <c r="X1227" s="61"/>
+      <c r="Y1227" s="61"/>
+      <c r="Z1227" s="61"/>
+      <c r="AA1227" s="61"/>
+      <c r="AB1227" s="61"/>
+      <c r="AC1227" s="61"/>
+      <c r="AD1227" s="61"/>
+      <c r="AE1227" s="61"/>
+      <c r="AF1227" s="61"/>
+      <c r="AG1227" s="61"/>
     </row>
     <row r="1228" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1229" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31368,38 +30990,38 @@
     <row r="1388" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1389" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1390" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1390" s="62"/>
-      <c r="C1390" s="62"/>
-      <c r="D1390" s="62"/>
-      <c r="E1390" s="62"/>
-      <c r="F1390" s="62"/>
-      <c r="G1390" s="62"/>
-      <c r="H1390" s="62"/>
-      <c r="I1390" s="62"/>
-      <c r="J1390" s="62"/>
-      <c r="K1390" s="62"/>
-      <c r="L1390" s="62"/>
-      <c r="M1390" s="62"/>
-      <c r="N1390" s="62"/>
-      <c r="O1390" s="62"/>
-      <c r="P1390" s="62"/>
-      <c r="Q1390" s="62"/>
-      <c r="R1390" s="62"/>
-      <c r="S1390" s="62"/>
-      <c r="T1390" s="62"/>
-      <c r="U1390" s="62"/>
-      <c r="V1390" s="62"/>
-      <c r="W1390" s="62"/>
-      <c r="X1390" s="62"/>
-      <c r="Y1390" s="62"/>
-      <c r="Z1390" s="62"/>
-      <c r="AA1390" s="62"/>
-      <c r="AB1390" s="62"/>
-      <c r="AC1390" s="62"/>
-      <c r="AD1390" s="62"/>
-      <c r="AE1390" s="62"/>
-      <c r="AF1390" s="62"/>
-      <c r="AG1390" s="62"/>
+      <c r="B1390" s="61"/>
+      <c r="C1390" s="61"/>
+      <c r="D1390" s="61"/>
+      <c r="E1390" s="61"/>
+      <c r="F1390" s="61"/>
+      <c r="G1390" s="61"/>
+      <c r="H1390" s="61"/>
+      <c r="I1390" s="61"/>
+      <c r="J1390" s="61"/>
+      <c r="K1390" s="61"/>
+      <c r="L1390" s="61"/>
+      <c r="M1390" s="61"/>
+      <c r="N1390" s="61"/>
+      <c r="O1390" s="61"/>
+      <c r="P1390" s="61"/>
+      <c r="Q1390" s="61"/>
+      <c r="R1390" s="61"/>
+      <c r="S1390" s="61"/>
+      <c r="T1390" s="61"/>
+      <c r="U1390" s="61"/>
+      <c r="V1390" s="61"/>
+      <c r="W1390" s="61"/>
+      <c r="X1390" s="61"/>
+      <c r="Y1390" s="61"/>
+      <c r="Z1390" s="61"/>
+      <c r="AA1390" s="61"/>
+      <c r="AB1390" s="61"/>
+      <c r="AC1390" s="61"/>
+      <c r="AD1390" s="61"/>
+      <c r="AE1390" s="61"/>
+      <c r="AF1390" s="61"/>
+      <c r="AG1390" s="61"/>
     </row>
     <row r="1391" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1392" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31494,38 +31116,38 @@
     <row r="1500" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1501" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1502" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1502" s="62"/>
-      <c r="C1502" s="62"/>
-      <c r="D1502" s="62"/>
-      <c r="E1502" s="62"/>
-      <c r="F1502" s="62"/>
-      <c r="G1502" s="62"/>
-      <c r="H1502" s="62"/>
-      <c r="I1502" s="62"/>
-      <c r="J1502" s="62"/>
-      <c r="K1502" s="62"/>
-      <c r="L1502" s="62"/>
-      <c r="M1502" s="62"/>
-      <c r="N1502" s="62"/>
-      <c r="O1502" s="62"/>
-      <c r="P1502" s="62"/>
-      <c r="Q1502" s="62"/>
-      <c r="R1502" s="62"/>
-      <c r="S1502" s="62"/>
-      <c r="T1502" s="62"/>
-      <c r="U1502" s="62"/>
-      <c r="V1502" s="62"/>
-      <c r="W1502" s="62"/>
-      <c r="X1502" s="62"/>
-      <c r="Y1502" s="62"/>
-      <c r="Z1502" s="62"/>
-      <c r="AA1502" s="62"/>
-      <c r="AB1502" s="62"/>
-      <c r="AC1502" s="62"/>
-      <c r="AD1502" s="62"/>
-      <c r="AE1502" s="62"/>
-      <c r="AF1502" s="62"/>
-      <c r="AG1502" s="62"/>
+      <c r="B1502" s="61"/>
+      <c r="C1502" s="61"/>
+      <c r="D1502" s="61"/>
+      <c r="E1502" s="61"/>
+      <c r="F1502" s="61"/>
+      <c r="G1502" s="61"/>
+      <c r="H1502" s="61"/>
+      <c r="I1502" s="61"/>
+      <c r="J1502" s="61"/>
+      <c r="K1502" s="61"/>
+      <c r="L1502" s="61"/>
+      <c r="M1502" s="61"/>
+      <c r="N1502" s="61"/>
+      <c r="O1502" s="61"/>
+      <c r="P1502" s="61"/>
+      <c r="Q1502" s="61"/>
+      <c r="R1502" s="61"/>
+      <c r="S1502" s="61"/>
+      <c r="T1502" s="61"/>
+      <c r="U1502" s="61"/>
+      <c r="V1502" s="61"/>
+      <c r="W1502" s="61"/>
+      <c r="X1502" s="61"/>
+      <c r="Y1502" s="61"/>
+      <c r="Z1502" s="61"/>
+      <c r="AA1502" s="61"/>
+      <c r="AB1502" s="61"/>
+      <c r="AC1502" s="61"/>
+      <c r="AD1502" s="61"/>
+      <c r="AE1502" s="61"/>
+      <c r="AF1502" s="61"/>
+      <c r="AG1502" s="61"/>
     </row>
     <row r="1503" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1504" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31576,38 +31198,38 @@
     <row r="1602" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1603" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1604" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1604" s="62"/>
-      <c r="C1604" s="62"/>
-      <c r="D1604" s="62"/>
-      <c r="E1604" s="62"/>
-      <c r="F1604" s="62"/>
-      <c r="G1604" s="62"/>
-      <c r="H1604" s="62"/>
-      <c r="I1604" s="62"/>
-      <c r="J1604" s="62"/>
-      <c r="K1604" s="62"/>
-      <c r="L1604" s="62"/>
-      <c r="M1604" s="62"/>
-      <c r="N1604" s="62"/>
-      <c r="O1604" s="62"/>
-      <c r="P1604" s="62"/>
-      <c r="Q1604" s="62"/>
-      <c r="R1604" s="62"/>
-      <c r="S1604" s="62"/>
-      <c r="T1604" s="62"/>
-      <c r="U1604" s="62"/>
-      <c r="V1604" s="62"/>
-      <c r="W1604" s="62"/>
-      <c r="X1604" s="62"/>
-      <c r="Y1604" s="62"/>
-      <c r="Z1604" s="62"/>
-      <c r="AA1604" s="62"/>
-      <c r="AB1604" s="62"/>
-      <c r="AC1604" s="62"/>
-      <c r="AD1604" s="62"/>
-      <c r="AE1604" s="62"/>
-      <c r="AF1604" s="62"/>
-      <c r="AG1604" s="62"/>
+      <c r="B1604" s="61"/>
+      <c r="C1604" s="61"/>
+      <c r="D1604" s="61"/>
+      <c r="E1604" s="61"/>
+      <c r="F1604" s="61"/>
+      <c r="G1604" s="61"/>
+      <c r="H1604" s="61"/>
+      <c r="I1604" s="61"/>
+      <c r="J1604" s="61"/>
+      <c r="K1604" s="61"/>
+      <c r="L1604" s="61"/>
+      <c r="M1604" s="61"/>
+      <c r="N1604" s="61"/>
+      <c r="O1604" s="61"/>
+      <c r="P1604" s="61"/>
+      <c r="Q1604" s="61"/>
+      <c r="R1604" s="61"/>
+      <c r="S1604" s="61"/>
+      <c r="T1604" s="61"/>
+      <c r="U1604" s="61"/>
+      <c r="V1604" s="61"/>
+      <c r="W1604" s="61"/>
+      <c r="X1604" s="61"/>
+      <c r="Y1604" s="61"/>
+      <c r="Z1604" s="61"/>
+      <c r="AA1604" s="61"/>
+      <c r="AB1604" s="61"/>
+      <c r="AC1604" s="61"/>
+      <c r="AD1604" s="61"/>
+      <c r="AE1604" s="61"/>
+      <c r="AF1604" s="61"/>
+      <c r="AG1604" s="61"/>
     </row>
     <row r="1605" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1606" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31682,38 +31304,38 @@
     <row r="1695" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1697" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1698" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1698" s="62"/>
-      <c r="C1698" s="62"/>
-      <c r="D1698" s="62"/>
-      <c r="E1698" s="62"/>
-      <c r="F1698" s="62"/>
-      <c r="G1698" s="62"/>
-      <c r="H1698" s="62"/>
-      <c r="I1698" s="62"/>
-      <c r="J1698" s="62"/>
-      <c r="K1698" s="62"/>
-      <c r="L1698" s="62"/>
-      <c r="M1698" s="62"/>
-      <c r="N1698" s="62"/>
-      <c r="O1698" s="62"/>
-      <c r="P1698" s="62"/>
-      <c r="Q1698" s="62"/>
-      <c r="R1698" s="62"/>
-      <c r="S1698" s="62"/>
-      <c r="T1698" s="62"/>
-      <c r="U1698" s="62"/>
-      <c r="V1698" s="62"/>
-      <c r="W1698" s="62"/>
-      <c r="X1698" s="62"/>
-      <c r="Y1698" s="62"/>
-      <c r="Z1698" s="62"/>
-      <c r="AA1698" s="62"/>
-      <c r="AB1698" s="62"/>
-      <c r="AC1698" s="62"/>
-      <c r="AD1698" s="62"/>
-      <c r="AE1698" s="62"/>
-      <c r="AF1698" s="62"/>
-      <c r="AG1698" s="62"/>
+      <c r="B1698" s="61"/>
+      <c r="C1698" s="61"/>
+      <c r="D1698" s="61"/>
+      <c r="E1698" s="61"/>
+      <c r="F1698" s="61"/>
+      <c r="G1698" s="61"/>
+      <c r="H1698" s="61"/>
+      <c r="I1698" s="61"/>
+      <c r="J1698" s="61"/>
+      <c r="K1698" s="61"/>
+      <c r="L1698" s="61"/>
+      <c r="M1698" s="61"/>
+      <c r="N1698" s="61"/>
+      <c r="O1698" s="61"/>
+      <c r="P1698" s="61"/>
+      <c r="Q1698" s="61"/>
+      <c r="R1698" s="61"/>
+      <c r="S1698" s="61"/>
+      <c r="T1698" s="61"/>
+      <c r="U1698" s="61"/>
+      <c r="V1698" s="61"/>
+      <c r="W1698" s="61"/>
+      <c r="X1698" s="61"/>
+      <c r="Y1698" s="61"/>
+      <c r="Z1698" s="61"/>
+      <c r="AA1698" s="61"/>
+      <c r="AB1698" s="61"/>
+      <c r="AC1698" s="61"/>
+      <c r="AD1698" s="61"/>
+      <c r="AE1698" s="61"/>
+      <c r="AF1698" s="61"/>
+      <c r="AG1698" s="61"/>
     </row>
     <row r="1699" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1700" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31824,38 +31446,38 @@
     <row r="1943" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1944" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1945" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1945" s="62"/>
-      <c r="C1945" s="62"/>
-      <c r="D1945" s="62"/>
-      <c r="E1945" s="62"/>
-      <c r="F1945" s="62"/>
-      <c r="G1945" s="62"/>
-      <c r="H1945" s="62"/>
-      <c r="I1945" s="62"/>
-      <c r="J1945" s="62"/>
-      <c r="K1945" s="62"/>
-      <c r="L1945" s="62"/>
-      <c r="M1945" s="62"/>
-      <c r="N1945" s="62"/>
-      <c r="O1945" s="62"/>
-      <c r="P1945" s="62"/>
-      <c r="Q1945" s="62"/>
-      <c r="R1945" s="62"/>
-      <c r="S1945" s="62"/>
-      <c r="T1945" s="62"/>
-      <c r="U1945" s="62"/>
-      <c r="V1945" s="62"/>
-      <c r="W1945" s="62"/>
-      <c r="X1945" s="62"/>
-      <c r="Y1945" s="62"/>
-      <c r="Z1945" s="62"/>
-      <c r="AA1945" s="62"/>
-      <c r="AB1945" s="62"/>
-      <c r="AC1945" s="62"/>
-      <c r="AD1945" s="62"/>
-      <c r="AE1945" s="62"/>
-      <c r="AF1945" s="62"/>
-      <c r="AG1945" s="62"/>
+      <c r="B1945" s="61"/>
+      <c r="C1945" s="61"/>
+      <c r="D1945" s="61"/>
+      <c r="E1945" s="61"/>
+      <c r="F1945" s="61"/>
+      <c r="G1945" s="61"/>
+      <c r="H1945" s="61"/>
+      <c r="I1945" s="61"/>
+      <c r="J1945" s="61"/>
+      <c r="K1945" s="61"/>
+      <c r="L1945" s="61"/>
+      <c r="M1945" s="61"/>
+      <c r="N1945" s="61"/>
+      <c r="O1945" s="61"/>
+      <c r="P1945" s="61"/>
+      <c r="Q1945" s="61"/>
+      <c r="R1945" s="61"/>
+      <c r="S1945" s="61"/>
+      <c r="T1945" s="61"/>
+      <c r="U1945" s="61"/>
+      <c r="V1945" s="61"/>
+      <c r="W1945" s="61"/>
+      <c r="X1945" s="61"/>
+      <c r="Y1945" s="61"/>
+      <c r="Z1945" s="61"/>
+      <c r="AA1945" s="61"/>
+      <c r="AB1945" s="61"/>
+      <c r="AC1945" s="61"/>
+      <c r="AD1945" s="61"/>
+      <c r="AE1945" s="61"/>
+      <c r="AF1945" s="61"/>
+      <c r="AG1945" s="61"/>
     </row>
     <row r="1946" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1947" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31916,38 +31538,38 @@
     <row r="2029" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2030" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2031" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2031" s="62"/>
-      <c r="C2031" s="62"/>
-      <c r="D2031" s="62"/>
-      <c r="E2031" s="62"/>
-      <c r="F2031" s="62"/>
-      <c r="G2031" s="62"/>
-      <c r="H2031" s="62"/>
-      <c r="I2031" s="62"/>
-      <c r="J2031" s="62"/>
-      <c r="K2031" s="62"/>
-      <c r="L2031" s="62"/>
-      <c r="M2031" s="62"/>
-      <c r="N2031" s="62"/>
-      <c r="O2031" s="62"/>
-      <c r="P2031" s="62"/>
-      <c r="Q2031" s="62"/>
-      <c r="R2031" s="62"/>
-      <c r="S2031" s="62"/>
-      <c r="T2031" s="62"/>
-      <c r="U2031" s="62"/>
-      <c r="V2031" s="62"/>
-      <c r="W2031" s="62"/>
-      <c r="X2031" s="62"/>
-      <c r="Y2031" s="62"/>
-      <c r="Z2031" s="62"/>
-      <c r="AA2031" s="62"/>
-      <c r="AB2031" s="62"/>
-      <c r="AC2031" s="62"/>
-      <c r="AD2031" s="62"/>
-      <c r="AE2031" s="62"/>
-      <c r="AF2031" s="62"/>
-      <c r="AG2031" s="62"/>
+      <c r="B2031" s="61"/>
+      <c r="C2031" s="61"/>
+      <c r="D2031" s="61"/>
+      <c r="E2031" s="61"/>
+      <c r="F2031" s="61"/>
+      <c r="G2031" s="61"/>
+      <c r="H2031" s="61"/>
+      <c r="I2031" s="61"/>
+      <c r="J2031" s="61"/>
+      <c r="K2031" s="61"/>
+      <c r="L2031" s="61"/>
+      <c r="M2031" s="61"/>
+      <c r="N2031" s="61"/>
+      <c r="O2031" s="61"/>
+      <c r="P2031" s="61"/>
+      <c r="Q2031" s="61"/>
+      <c r="R2031" s="61"/>
+      <c r="S2031" s="61"/>
+      <c r="T2031" s="61"/>
+      <c r="U2031" s="61"/>
+      <c r="V2031" s="61"/>
+      <c r="W2031" s="61"/>
+      <c r="X2031" s="61"/>
+      <c r="Y2031" s="61"/>
+      <c r="Z2031" s="61"/>
+      <c r="AA2031" s="61"/>
+      <c r="AB2031" s="61"/>
+      <c r="AC2031" s="61"/>
+      <c r="AD2031" s="61"/>
+      <c r="AE2031" s="61"/>
+      <c r="AF2031" s="61"/>
+      <c r="AG2031" s="61"/>
     </row>
     <row r="2032" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2033" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32016,38 +31638,38 @@
     <row r="2151" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2152" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2153" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2153" s="62"/>
-      <c r="C2153" s="62"/>
-      <c r="D2153" s="62"/>
-      <c r="E2153" s="62"/>
-      <c r="F2153" s="62"/>
-      <c r="G2153" s="62"/>
-      <c r="H2153" s="62"/>
-      <c r="I2153" s="62"/>
-      <c r="J2153" s="62"/>
-      <c r="K2153" s="62"/>
-      <c r="L2153" s="62"/>
-      <c r="M2153" s="62"/>
-      <c r="N2153" s="62"/>
-      <c r="O2153" s="62"/>
-      <c r="P2153" s="62"/>
-      <c r="Q2153" s="62"/>
-      <c r="R2153" s="62"/>
-      <c r="S2153" s="62"/>
-      <c r="T2153" s="62"/>
-      <c r="U2153" s="62"/>
-      <c r="V2153" s="62"/>
-      <c r="W2153" s="62"/>
-      <c r="X2153" s="62"/>
-      <c r="Y2153" s="62"/>
-      <c r="Z2153" s="62"/>
-      <c r="AA2153" s="62"/>
-      <c r="AB2153" s="62"/>
-      <c r="AC2153" s="62"/>
-      <c r="AD2153" s="62"/>
-      <c r="AE2153" s="62"/>
-      <c r="AF2153" s="62"/>
-      <c r="AG2153" s="62"/>
+      <c r="B2153" s="61"/>
+      <c r="C2153" s="61"/>
+      <c r="D2153" s="61"/>
+      <c r="E2153" s="61"/>
+      <c r="F2153" s="61"/>
+      <c r="G2153" s="61"/>
+      <c r="H2153" s="61"/>
+      <c r="I2153" s="61"/>
+      <c r="J2153" s="61"/>
+      <c r="K2153" s="61"/>
+      <c r="L2153" s="61"/>
+      <c r="M2153" s="61"/>
+      <c r="N2153" s="61"/>
+      <c r="O2153" s="61"/>
+      <c r="P2153" s="61"/>
+      <c r="Q2153" s="61"/>
+      <c r="R2153" s="61"/>
+      <c r="S2153" s="61"/>
+      <c r="T2153" s="61"/>
+      <c r="U2153" s="61"/>
+      <c r="V2153" s="61"/>
+      <c r="W2153" s="61"/>
+      <c r="X2153" s="61"/>
+      <c r="Y2153" s="61"/>
+      <c r="Z2153" s="61"/>
+      <c r="AA2153" s="61"/>
+      <c r="AB2153" s="61"/>
+      <c r="AC2153" s="61"/>
+      <c r="AD2153" s="61"/>
+      <c r="AE2153" s="61"/>
+      <c r="AF2153" s="61"/>
+      <c r="AG2153" s="61"/>
     </row>
     <row r="2154" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2155" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32115,38 +31737,38 @@
     <row r="2315" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2316" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2317" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2317" s="62"/>
-      <c r="C2317" s="62"/>
-      <c r="D2317" s="62"/>
-      <c r="E2317" s="62"/>
-      <c r="F2317" s="62"/>
-      <c r="G2317" s="62"/>
-      <c r="H2317" s="62"/>
-      <c r="I2317" s="62"/>
-      <c r="J2317" s="62"/>
-      <c r="K2317" s="62"/>
-      <c r="L2317" s="62"/>
-      <c r="M2317" s="62"/>
-      <c r="N2317" s="62"/>
-      <c r="O2317" s="62"/>
-      <c r="P2317" s="62"/>
-      <c r="Q2317" s="62"/>
-      <c r="R2317" s="62"/>
-      <c r="S2317" s="62"/>
-      <c r="T2317" s="62"/>
-      <c r="U2317" s="62"/>
-      <c r="V2317" s="62"/>
-      <c r="W2317" s="62"/>
-      <c r="X2317" s="62"/>
-      <c r="Y2317" s="62"/>
-      <c r="Z2317" s="62"/>
-      <c r="AA2317" s="62"/>
-      <c r="AB2317" s="62"/>
-      <c r="AC2317" s="62"/>
-      <c r="AD2317" s="62"/>
-      <c r="AE2317" s="62"/>
-      <c r="AF2317" s="62"/>
-      <c r="AG2317" s="62"/>
+      <c r="B2317" s="61"/>
+      <c r="C2317" s="61"/>
+      <c r="D2317" s="61"/>
+      <c r="E2317" s="61"/>
+      <c r="F2317" s="61"/>
+      <c r="G2317" s="61"/>
+      <c r="H2317" s="61"/>
+      <c r="I2317" s="61"/>
+      <c r="J2317" s="61"/>
+      <c r="K2317" s="61"/>
+      <c r="L2317" s="61"/>
+      <c r="M2317" s="61"/>
+      <c r="N2317" s="61"/>
+      <c r="O2317" s="61"/>
+      <c r="P2317" s="61"/>
+      <c r="Q2317" s="61"/>
+      <c r="R2317" s="61"/>
+      <c r="S2317" s="61"/>
+      <c r="T2317" s="61"/>
+      <c r="U2317" s="61"/>
+      <c r="V2317" s="61"/>
+      <c r="W2317" s="61"/>
+      <c r="X2317" s="61"/>
+      <c r="Y2317" s="61"/>
+      <c r="Z2317" s="61"/>
+      <c r="AA2317" s="61"/>
+      <c r="AB2317" s="61"/>
+      <c r="AC2317" s="61"/>
+      <c r="AD2317" s="61"/>
+      <c r="AE2317" s="61"/>
+      <c r="AF2317" s="61"/>
+      <c r="AG2317" s="61"/>
     </row>
     <row r="2318" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2319" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32229,38 +31851,38 @@
     <row r="2417" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2418" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2419" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2419" s="62"/>
-      <c r="C2419" s="62"/>
-      <c r="D2419" s="62"/>
-      <c r="E2419" s="62"/>
-      <c r="F2419" s="62"/>
-      <c r="G2419" s="62"/>
-      <c r="H2419" s="62"/>
-      <c r="I2419" s="62"/>
-      <c r="J2419" s="62"/>
-      <c r="K2419" s="62"/>
-      <c r="L2419" s="62"/>
-      <c r="M2419" s="62"/>
-      <c r="N2419" s="62"/>
-      <c r="O2419" s="62"/>
-      <c r="P2419" s="62"/>
-      <c r="Q2419" s="62"/>
-      <c r="R2419" s="62"/>
-      <c r="S2419" s="62"/>
-      <c r="T2419" s="62"/>
-      <c r="U2419" s="62"/>
-      <c r="V2419" s="62"/>
-      <c r="W2419" s="62"/>
-      <c r="X2419" s="62"/>
-      <c r="Y2419" s="62"/>
-      <c r="Z2419" s="62"/>
-      <c r="AA2419" s="62"/>
-      <c r="AB2419" s="62"/>
-      <c r="AC2419" s="62"/>
-      <c r="AD2419" s="62"/>
-      <c r="AE2419" s="62"/>
-      <c r="AF2419" s="62"/>
-      <c r="AG2419" s="62"/>
+      <c r="B2419" s="61"/>
+      <c r="C2419" s="61"/>
+      <c r="D2419" s="61"/>
+      <c r="E2419" s="61"/>
+      <c r="F2419" s="61"/>
+      <c r="G2419" s="61"/>
+      <c r="H2419" s="61"/>
+      <c r="I2419" s="61"/>
+      <c r="J2419" s="61"/>
+      <c r="K2419" s="61"/>
+      <c r="L2419" s="61"/>
+      <c r="M2419" s="61"/>
+      <c r="N2419" s="61"/>
+      <c r="O2419" s="61"/>
+      <c r="P2419" s="61"/>
+      <c r="Q2419" s="61"/>
+      <c r="R2419" s="61"/>
+      <c r="S2419" s="61"/>
+      <c r="T2419" s="61"/>
+      <c r="U2419" s="61"/>
+      <c r="V2419" s="61"/>
+      <c r="W2419" s="61"/>
+      <c r="X2419" s="61"/>
+      <c r="Y2419" s="61"/>
+      <c r="Z2419" s="61"/>
+      <c r="AA2419" s="61"/>
+      <c r="AB2419" s="61"/>
+      <c r="AC2419" s="61"/>
+      <c r="AD2419" s="61"/>
+      <c r="AE2419" s="61"/>
+      <c r="AF2419" s="61"/>
+      <c r="AG2419" s="61"/>
     </row>
     <row r="2420" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2421" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32329,38 +31951,38 @@
     <row r="2507" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2508" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2509" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2509" s="62"/>
-      <c r="C2509" s="62"/>
-      <c r="D2509" s="62"/>
-      <c r="E2509" s="62"/>
-      <c r="F2509" s="62"/>
-      <c r="G2509" s="62"/>
-      <c r="H2509" s="62"/>
-      <c r="I2509" s="62"/>
-      <c r="J2509" s="62"/>
-      <c r="K2509" s="62"/>
-      <c r="L2509" s="62"/>
-      <c r="M2509" s="62"/>
-      <c r="N2509" s="62"/>
-      <c r="O2509" s="62"/>
-      <c r="P2509" s="62"/>
-      <c r="Q2509" s="62"/>
-      <c r="R2509" s="62"/>
-      <c r="S2509" s="62"/>
-      <c r="T2509" s="62"/>
-      <c r="U2509" s="62"/>
-      <c r="V2509" s="62"/>
-      <c r="W2509" s="62"/>
-      <c r="X2509" s="62"/>
-      <c r="Y2509" s="62"/>
-      <c r="Z2509" s="62"/>
-      <c r="AA2509" s="62"/>
-      <c r="AB2509" s="62"/>
-      <c r="AC2509" s="62"/>
-      <c r="AD2509" s="62"/>
-      <c r="AE2509" s="62"/>
-      <c r="AF2509" s="62"/>
-      <c r="AG2509" s="62"/>
+      <c r="B2509" s="61"/>
+      <c r="C2509" s="61"/>
+      <c r="D2509" s="61"/>
+      <c r="E2509" s="61"/>
+      <c r="F2509" s="61"/>
+      <c r="G2509" s="61"/>
+      <c r="H2509" s="61"/>
+      <c r="I2509" s="61"/>
+      <c r="J2509" s="61"/>
+      <c r="K2509" s="61"/>
+      <c r="L2509" s="61"/>
+      <c r="M2509" s="61"/>
+      <c r="N2509" s="61"/>
+      <c r="O2509" s="61"/>
+      <c r="P2509" s="61"/>
+      <c r="Q2509" s="61"/>
+      <c r="R2509" s="61"/>
+      <c r="S2509" s="61"/>
+      <c r="T2509" s="61"/>
+      <c r="U2509" s="61"/>
+      <c r="V2509" s="61"/>
+      <c r="W2509" s="61"/>
+      <c r="X2509" s="61"/>
+      <c r="Y2509" s="61"/>
+      <c r="Z2509" s="61"/>
+      <c r="AA2509" s="61"/>
+      <c r="AB2509" s="61"/>
+      <c r="AC2509" s="61"/>
+      <c r="AD2509" s="61"/>
+      <c r="AE2509" s="61"/>
+      <c r="AF2509" s="61"/>
+      <c r="AG2509" s="61"/>
     </row>
     <row r="2510" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2511" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32425,38 +32047,38 @@
     <row r="2596" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2597" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2598" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2598" s="62"/>
-      <c r="C2598" s="62"/>
-      <c r="D2598" s="62"/>
-      <c r="E2598" s="62"/>
-      <c r="F2598" s="62"/>
-      <c r="G2598" s="62"/>
-      <c r="H2598" s="62"/>
-      <c r="I2598" s="62"/>
-      <c r="J2598" s="62"/>
-      <c r="K2598" s="62"/>
-      <c r="L2598" s="62"/>
-      <c r="M2598" s="62"/>
-      <c r="N2598" s="62"/>
-      <c r="O2598" s="62"/>
-      <c r="P2598" s="62"/>
-      <c r="Q2598" s="62"/>
-      <c r="R2598" s="62"/>
-      <c r="S2598" s="62"/>
-      <c r="T2598" s="62"/>
-      <c r="U2598" s="62"/>
-      <c r="V2598" s="62"/>
-      <c r="W2598" s="62"/>
-      <c r="X2598" s="62"/>
-      <c r="Y2598" s="62"/>
-      <c r="Z2598" s="62"/>
-      <c r="AA2598" s="62"/>
-      <c r="AB2598" s="62"/>
-      <c r="AC2598" s="62"/>
-      <c r="AD2598" s="62"/>
-      <c r="AE2598" s="62"/>
-      <c r="AF2598" s="62"/>
-      <c r="AG2598" s="62"/>
+      <c r="B2598" s="61"/>
+      <c r="C2598" s="61"/>
+      <c r="D2598" s="61"/>
+      <c r="E2598" s="61"/>
+      <c r="F2598" s="61"/>
+      <c r="G2598" s="61"/>
+      <c r="H2598" s="61"/>
+      <c r="I2598" s="61"/>
+      <c r="J2598" s="61"/>
+      <c r="K2598" s="61"/>
+      <c r="L2598" s="61"/>
+      <c r="M2598" s="61"/>
+      <c r="N2598" s="61"/>
+      <c r="O2598" s="61"/>
+      <c r="P2598" s="61"/>
+      <c r="Q2598" s="61"/>
+      <c r="R2598" s="61"/>
+      <c r="S2598" s="61"/>
+      <c r="T2598" s="61"/>
+      <c r="U2598" s="61"/>
+      <c r="V2598" s="61"/>
+      <c r="W2598" s="61"/>
+      <c r="X2598" s="61"/>
+      <c r="Y2598" s="61"/>
+      <c r="Z2598" s="61"/>
+      <c r="AA2598" s="61"/>
+      <c r="AB2598" s="61"/>
+      <c r="AC2598" s="61"/>
+      <c r="AD2598" s="61"/>
+      <c r="AE2598" s="61"/>
+      <c r="AF2598" s="61"/>
+      <c r="AG2598" s="61"/>
     </row>
     <row r="2599" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2600" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32564,38 +32186,38 @@
     <row r="2717" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2718" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2719" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2719" s="62"/>
-      <c r="C2719" s="62"/>
-      <c r="D2719" s="62"/>
-      <c r="E2719" s="62"/>
-      <c r="F2719" s="62"/>
-      <c r="G2719" s="62"/>
-      <c r="H2719" s="62"/>
-      <c r="I2719" s="62"/>
-      <c r="J2719" s="62"/>
-      <c r="K2719" s="62"/>
-      <c r="L2719" s="62"/>
-      <c r="M2719" s="62"/>
-      <c r="N2719" s="62"/>
-      <c r="O2719" s="62"/>
-      <c r="P2719" s="62"/>
-      <c r="Q2719" s="62"/>
-      <c r="R2719" s="62"/>
-      <c r="S2719" s="62"/>
-      <c r="T2719" s="62"/>
-      <c r="U2719" s="62"/>
-      <c r="V2719" s="62"/>
-      <c r="W2719" s="62"/>
-      <c r="X2719" s="62"/>
-      <c r="Y2719" s="62"/>
-      <c r="Z2719" s="62"/>
-      <c r="AA2719" s="62"/>
-      <c r="AB2719" s="62"/>
-      <c r="AC2719" s="62"/>
-      <c r="AD2719" s="62"/>
-      <c r="AE2719" s="62"/>
-      <c r="AF2719" s="62"/>
-      <c r="AG2719" s="62"/>
+      <c r="B2719" s="61"/>
+      <c r="C2719" s="61"/>
+      <c r="D2719" s="61"/>
+      <c r="E2719" s="61"/>
+      <c r="F2719" s="61"/>
+      <c r="G2719" s="61"/>
+      <c r="H2719" s="61"/>
+      <c r="I2719" s="61"/>
+      <c r="J2719" s="61"/>
+      <c r="K2719" s="61"/>
+      <c r="L2719" s="61"/>
+      <c r="M2719" s="61"/>
+      <c r="N2719" s="61"/>
+      <c r="O2719" s="61"/>
+      <c r="P2719" s="61"/>
+      <c r="Q2719" s="61"/>
+      <c r="R2719" s="61"/>
+      <c r="S2719" s="61"/>
+      <c r="T2719" s="61"/>
+      <c r="U2719" s="61"/>
+      <c r="V2719" s="61"/>
+      <c r="W2719" s="61"/>
+      <c r="X2719" s="61"/>
+      <c r="Y2719" s="61"/>
+      <c r="Z2719" s="61"/>
+      <c r="AA2719" s="61"/>
+      <c r="AB2719" s="61"/>
+      <c r="AC2719" s="61"/>
+      <c r="AD2719" s="61"/>
+      <c r="AE2719" s="61"/>
+      <c r="AF2719" s="61"/>
+      <c r="AG2719" s="61"/>
     </row>
     <row r="2720" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2721" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32676,38 +32298,38 @@
     <row r="2835" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2836" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2837" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2837" s="62"/>
-      <c r="C2837" s="62"/>
-      <c r="D2837" s="62"/>
-      <c r="E2837" s="62"/>
-      <c r="F2837" s="62"/>
-      <c r="G2837" s="62"/>
-      <c r="H2837" s="62"/>
-      <c r="I2837" s="62"/>
-      <c r="J2837" s="62"/>
-      <c r="K2837" s="62"/>
-      <c r="L2837" s="62"/>
-      <c r="M2837" s="62"/>
-      <c r="N2837" s="62"/>
-      <c r="O2837" s="62"/>
-      <c r="P2837" s="62"/>
-      <c r="Q2837" s="62"/>
-      <c r="R2837" s="62"/>
-      <c r="S2837" s="62"/>
-      <c r="T2837" s="62"/>
-      <c r="U2837" s="62"/>
-      <c r="V2837" s="62"/>
-      <c r="W2837" s="62"/>
-      <c r="X2837" s="62"/>
-      <c r="Y2837" s="62"/>
-      <c r="Z2837" s="62"/>
-      <c r="AA2837" s="62"/>
-      <c r="AB2837" s="62"/>
-      <c r="AC2837" s="62"/>
-      <c r="AD2837" s="62"/>
-      <c r="AE2837" s="62"/>
-      <c r="AF2837" s="62"/>
-      <c r="AG2837" s="62"/>
+      <c r="B2837" s="61"/>
+      <c r="C2837" s="61"/>
+      <c r="D2837" s="61"/>
+      <c r="E2837" s="61"/>
+      <c r="F2837" s="61"/>
+      <c r="G2837" s="61"/>
+      <c r="H2837" s="61"/>
+      <c r="I2837" s="61"/>
+      <c r="J2837" s="61"/>
+      <c r="K2837" s="61"/>
+      <c r="L2837" s="61"/>
+      <c r="M2837" s="61"/>
+      <c r="N2837" s="61"/>
+      <c r="O2837" s="61"/>
+      <c r="P2837" s="61"/>
+      <c r="Q2837" s="61"/>
+      <c r="R2837" s="61"/>
+      <c r="S2837" s="61"/>
+      <c r="T2837" s="61"/>
+      <c r="U2837" s="61"/>
+      <c r="V2837" s="61"/>
+      <c r="W2837" s="61"/>
+      <c r="X2837" s="61"/>
+      <c r="Y2837" s="61"/>
+      <c r="Z2837" s="61"/>
+      <c r="AA2837" s="61"/>
+      <c r="AB2837" s="61"/>
+      <c r="AC2837" s="61"/>
+      <c r="AD2837" s="61"/>
+      <c r="AE2837" s="61"/>
+      <c r="AF2837" s="61"/>
+      <c r="AG2837" s="61"/>
     </row>
     <row r="2838" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2839" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -32715,6 +32337,13 @@
     <row r="2841" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2837:AG2837"/>
+    <mergeCell ref="B2153:AG2153"/>
+    <mergeCell ref="B2317:AG2317"/>
+    <mergeCell ref="B2419:AG2419"/>
+    <mergeCell ref="B2509:AG2509"/>
+    <mergeCell ref="B2598:AG2598"/>
+    <mergeCell ref="B2719:AG2719"/>
     <mergeCell ref="B2031:AG2031"/>
     <mergeCell ref="B308:AG308"/>
     <mergeCell ref="B511:AG511"/>
@@ -32727,13 +32356,6 @@
     <mergeCell ref="B1604:AG1604"/>
     <mergeCell ref="B1698:AG1698"/>
     <mergeCell ref="B1945:AG1945"/>
-    <mergeCell ref="B2837:AG2837"/>
-    <mergeCell ref="B2153:AG2153"/>
-    <mergeCell ref="B2317:AG2317"/>
-    <mergeCell ref="B2419:AG2419"/>
-    <mergeCell ref="B2509:AG2509"/>
-    <mergeCell ref="B2598:AG2598"/>
-    <mergeCell ref="B2719:AG2719"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40516,103 +40138,103 @@
       <c r="A112" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B112" s="63" t="s">
+      <c r="B112" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C112" s="64">
+      <c r="C112" s="63">
         <v>12.999203</v>
       </c>
-      <c r="D112" s="64">
+      <c r="D112" s="63">
         <v>13.756338</v>
       </c>
-      <c r="E112" s="64">
+      <c r="E112" s="63">
         <v>14.272468</v>
       </c>
-      <c r="F112" s="64">
+      <c r="F112" s="63">
         <v>13.87274</v>
       </c>
-      <c r="G112" s="64">
+      <c r="G112" s="63">
         <v>13.379066999999999</v>
       </c>
-      <c r="H112" s="64">
+      <c r="H112" s="63">
         <v>13.404615</v>
       </c>
-      <c r="I112" s="64">
+      <c r="I112" s="63">
         <v>13.498896999999999</v>
       </c>
-      <c r="J112" s="64">
+      <c r="J112" s="63">
         <v>13.628196000000001</v>
       </c>
-      <c r="K112" s="64">
+      <c r="K112" s="63">
         <v>13.736962</v>
       </c>
-      <c r="L112" s="64">
+      <c r="L112" s="63">
         <v>13.932218000000001</v>
       </c>
-      <c r="M112" s="64">
+      <c r="M112" s="63">
         <v>14.950908999999999</v>
       </c>
-      <c r="N112" s="64">
+      <c r="N112" s="63">
         <v>15.044097000000001</v>
       </c>
-      <c r="O112" s="64">
+      <c r="O112" s="63">
         <v>15.321702</v>
       </c>
-      <c r="P112" s="64">
+      <c r="P112" s="63">
         <v>15.516894000000001</v>
       </c>
-      <c r="Q112" s="64">
+      <c r="Q112" s="63">
         <v>15.691060999999999</v>
       </c>
-      <c r="R112" s="64">
+      <c r="R112" s="63">
         <v>15.773815000000001</v>
       </c>
-      <c r="S112" s="64">
+      <c r="S112" s="63">
         <v>15.950137</v>
       </c>
-      <c r="T112" s="64">
+      <c r="T112" s="63">
         <v>16.117809000000001</v>
       </c>
-      <c r="U112" s="64">
+      <c r="U112" s="63">
         <v>16.291615</v>
       </c>
-      <c r="V112" s="64">
+      <c r="V112" s="63">
         <v>16.466549000000001</v>
       </c>
-      <c r="W112" s="64">
+      <c r="W112" s="63">
         <v>16.700437999999998</v>
       </c>
-      <c r="X112" s="64">
+      <c r="X112" s="63">
         <v>16.943705000000001</v>
       </c>
-      <c r="Y112" s="64">
+      <c r="Y112" s="63">
         <v>17.277073000000001</v>
       </c>
-      <c r="Z112" s="64">
+      <c r="Z112" s="63">
         <v>17.574244</v>
       </c>
-      <c r="AA112" s="64">
+      <c r="AA112" s="63">
         <v>17.982026999999999</v>
       </c>
-      <c r="AB112" s="64">
+      <c r="AB112" s="63">
         <v>18.336407000000001</v>
       </c>
-      <c r="AC112" s="64">
+      <c r="AC112" s="63">
         <v>18.741672999999999</v>
       </c>
-      <c r="AD112" s="64">
+      <c r="AD112" s="63">
         <v>19.208071</v>
       </c>
-      <c r="AE112" s="64">
+      <c r="AE112" s="63">
         <v>19.600466000000001</v>
       </c>
-      <c r="AF112" s="64">
+      <c r="AF112" s="63">
         <v>20.057380999999999</v>
       </c>
-      <c r="AG112" s="64">
+      <c r="AG112" s="63">
         <v>20.632099</v>
       </c>
-      <c r="AH112" s="65">
+      <c r="AH112" s="64">
         <v>1.5518000000000001E-2</v>
       </c>
     </row>
@@ -43134,40 +42756,40 @@
     </row>
     <row r="145" spans="2:34" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="146" spans="2:34" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B146" s="66" t="s">
+      <c r="B146" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="C146" s="67"/>
-      <c r="D146" s="67"/>
-      <c r="E146" s="67"/>
-      <c r="F146" s="67"/>
-      <c r="G146" s="67"/>
-      <c r="H146" s="67"/>
-      <c r="I146" s="67"/>
-      <c r="J146" s="67"/>
-      <c r="K146" s="67"/>
-      <c r="L146" s="67"/>
-      <c r="M146" s="67"/>
-      <c r="N146" s="67"/>
-      <c r="O146" s="67"/>
-      <c r="P146" s="67"/>
-      <c r="Q146" s="67"/>
-      <c r="R146" s="67"/>
-      <c r="S146" s="67"/>
-      <c r="T146" s="67"/>
-      <c r="U146" s="67"/>
-      <c r="V146" s="67"/>
-      <c r="W146" s="67"/>
-      <c r="X146" s="67"/>
-      <c r="Y146" s="67"/>
-      <c r="Z146" s="67"/>
-      <c r="AA146" s="67"/>
-      <c r="AB146" s="67"/>
-      <c r="AC146" s="67"/>
-      <c r="AD146" s="67"/>
-      <c r="AE146" s="67"/>
-      <c r="AF146" s="67"/>
-      <c r="AG146" s="67"/>
+      <c r="C146" s="66"/>
+      <c r="D146" s="66"/>
+      <c r="E146" s="66"/>
+      <c r="F146" s="66"/>
+      <c r="G146" s="66"/>
+      <c r="H146" s="66"/>
+      <c r="I146" s="66"/>
+      <c r="J146" s="66"/>
+      <c r="K146" s="66"/>
+      <c r="L146" s="66"/>
+      <c r="M146" s="66"/>
+      <c r="N146" s="66"/>
+      <c r="O146" s="66"/>
+      <c r="P146" s="66"/>
+      <c r="Q146" s="66"/>
+      <c r="R146" s="66"/>
+      <c r="S146" s="66"/>
+      <c r="T146" s="66"/>
+      <c r="U146" s="66"/>
+      <c r="V146" s="66"/>
+      <c r="W146" s="66"/>
+      <c r="X146" s="66"/>
+      <c r="Y146" s="66"/>
+      <c r="Z146" s="66"/>
+      <c r="AA146" s="66"/>
+      <c r="AB146" s="66"/>
+      <c r="AC146" s="66"/>
+      <c r="AD146" s="66"/>
+      <c r="AE146" s="66"/>
+      <c r="AF146" s="66"/>
+      <c r="AG146" s="66"/>
       <c r="AH146" s="27"/>
     </row>
     <row r="147" spans="2:34" ht="14.4" x14ac:dyDescent="0.3">
@@ -43241,693 +42863,693 @@
       </c>
     </row>
     <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B308" s="62"/>
-      <c r="C308" s="62"/>
-      <c r="D308" s="62"/>
-      <c r="E308" s="62"/>
-      <c r="F308" s="62"/>
-      <c r="G308" s="62"/>
-      <c r="H308" s="62"/>
-      <c r="I308" s="62"/>
-      <c r="J308" s="62"/>
-      <c r="K308" s="62"/>
-      <c r="L308" s="62"/>
-      <c r="M308" s="62"/>
-      <c r="N308" s="62"/>
-      <c r="O308" s="62"/>
-      <c r="P308" s="62"/>
-      <c r="Q308" s="62"/>
-      <c r="R308" s="62"/>
-      <c r="S308" s="62"/>
-      <c r="T308" s="62"/>
-      <c r="U308" s="62"/>
-      <c r="V308" s="62"/>
-      <c r="W308" s="62"/>
-      <c r="X308" s="62"/>
-      <c r="Y308" s="62"/>
-      <c r="Z308" s="62"/>
-      <c r="AA308" s="62"/>
-      <c r="AB308" s="62"/>
-      <c r="AC308" s="62"/>
-      <c r="AD308" s="62"/>
-      <c r="AE308" s="62"/>
-      <c r="AF308" s="62"/>
-      <c r="AG308" s="62"/>
-      <c r="AH308" s="62"/>
+      <c r="B308" s="61"/>
+      <c r="C308" s="61"/>
+      <c r="D308" s="61"/>
+      <c r="E308" s="61"/>
+      <c r="F308" s="61"/>
+      <c r="G308" s="61"/>
+      <c r="H308" s="61"/>
+      <c r="I308" s="61"/>
+      <c r="J308" s="61"/>
+      <c r="K308" s="61"/>
+      <c r="L308" s="61"/>
+      <c r="M308" s="61"/>
+      <c r="N308" s="61"/>
+      <c r="O308" s="61"/>
+      <c r="P308" s="61"/>
+      <c r="Q308" s="61"/>
+      <c r="R308" s="61"/>
+      <c r="S308" s="61"/>
+      <c r="T308" s="61"/>
+      <c r="U308" s="61"/>
+      <c r="V308" s="61"/>
+      <c r="W308" s="61"/>
+      <c r="X308" s="61"/>
+      <c r="Y308" s="61"/>
+      <c r="Z308" s="61"/>
+      <c r="AA308" s="61"/>
+      <c r="AB308" s="61"/>
+      <c r="AC308" s="61"/>
+      <c r="AD308" s="61"/>
+      <c r="AE308" s="61"/>
+      <c r="AF308" s="61"/>
+      <c r="AG308" s="61"/>
+      <c r="AH308" s="61"/>
     </row>
     <row r="511" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B511" s="62"/>
-      <c r="C511" s="62"/>
-      <c r="D511" s="62"/>
-      <c r="E511" s="62"/>
-      <c r="F511" s="62"/>
-      <c r="G511" s="62"/>
-      <c r="H511" s="62"/>
-      <c r="I511" s="62"/>
-      <c r="J511" s="62"/>
-      <c r="K511" s="62"/>
-      <c r="L511" s="62"/>
-      <c r="M511" s="62"/>
-      <c r="N511" s="62"/>
-      <c r="O511" s="62"/>
-      <c r="P511" s="62"/>
-      <c r="Q511" s="62"/>
-      <c r="R511" s="62"/>
-      <c r="S511" s="62"/>
-      <c r="T511" s="62"/>
-      <c r="U511" s="62"/>
-      <c r="V511" s="62"/>
-      <c r="W511" s="62"/>
-      <c r="X511" s="62"/>
-      <c r="Y511" s="62"/>
-      <c r="Z511" s="62"/>
-      <c r="AA511" s="62"/>
-      <c r="AB511" s="62"/>
-      <c r="AC511" s="62"/>
-      <c r="AD511" s="62"/>
-      <c r="AE511" s="62"/>
-      <c r="AF511" s="62"/>
-      <c r="AG511" s="62"/>
-      <c r="AH511" s="62"/>
+      <c r="B511" s="61"/>
+      <c r="C511" s="61"/>
+      <c r="D511" s="61"/>
+      <c r="E511" s="61"/>
+      <c r="F511" s="61"/>
+      <c r="G511" s="61"/>
+      <c r="H511" s="61"/>
+      <c r="I511" s="61"/>
+      <c r="J511" s="61"/>
+      <c r="K511" s="61"/>
+      <c r="L511" s="61"/>
+      <c r="M511" s="61"/>
+      <c r="N511" s="61"/>
+      <c r="O511" s="61"/>
+      <c r="P511" s="61"/>
+      <c r="Q511" s="61"/>
+      <c r="R511" s="61"/>
+      <c r="S511" s="61"/>
+      <c r="T511" s="61"/>
+      <c r="U511" s="61"/>
+      <c r="V511" s="61"/>
+      <c r="W511" s="61"/>
+      <c r="X511" s="61"/>
+      <c r="Y511" s="61"/>
+      <c r="Z511" s="61"/>
+      <c r="AA511" s="61"/>
+      <c r="AB511" s="61"/>
+      <c r="AC511" s="61"/>
+      <c r="AD511" s="61"/>
+      <c r="AE511" s="61"/>
+      <c r="AF511" s="61"/>
+      <c r="AG511" s="61"/>
+      <c r="AH511" s="61"/>
     </row>
     <row r="712" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B712" s="62"/>
-      <c r="C712" s="62"/>
-      <c r="D712" s="62"/>
-      <c r="E712" s="62"/>
-      <c r="F712" s="62"/>
-      <c r="G712" s="62"/>
-      <c r="H712" s="62"/>
-      <c r="I712" s="62"/>
-      <c r="J712" s="62"/>
-      <c r="K712" s="62"/>
-      <c r="L712" s="62"/>
-      <c r="M712" s="62"/>
-      <c r="N712" s="62"/>
-      <c r="O712" s="62"/>
-      <c r="P712" s="62"/>
-      <c r="Q712" s="62"/>
-      <c r="R712" s="62"/>
-      <c r="S712" s="62"/>
-      <c r="T712" s="62"/>
-      <c r="U712" s="62"/>
-      <c r="V712" s="62"/>
-      <c r="W712" s="62"/>
-      <c r="X712" s="62"/>
-      <c r="Y712" s="62"/>
-      <c r="Z712" s="62"/>
-      <c r="AA712" s="62"/>
-      <c r="AB712" s="62"/>
-      <c r="AC712" s="62"/>
-      <c r="AD712" s="62"/>
-      <c r="AE712" s="62"/>
-      <c r="AF712" s="62"/>
-      <c r="AG712" s="62"/>
-      <c r="AH712" s="62"/>
+      <c r="B712" s="61"/>
+      <c r="C712" s="61"/>
+      <c r="D712" s="61"/>
+      <c r="E712" s="61"/>
+      <c r="F712" s="61"/>
+      <c r="G712" s="61"/>
+      <c r="H712" s="61"/>
+      <c r="I712" s="61"/>
+      <c r="J712" s="61"/>
+      <c r="K712" s="61"/>
+      <c r="L712" s="61"/>
+      <c r="M712" s="61"/>
+      <c r="N712" s="61"/>
+      <c r="O712" s="61"/>
+      <c r="P712" s="61"/>
+      <c r="Q712" s="61"/>
+      <c r="R712" s="61"/>
+      <c r="S712" s="61"/>
+      <c r="T712" s="61"/>
+      <c r="U712" s="61"/>
+      <c r="V712" s="61"/>
+      <c r="W712" s="61"/>
+      <c r="X712" s="61"/>
+      <c r="Y712" s="61"/>
+      <c r="Z712" s="61"/>
+      <c r="AA712" s="61"/>
+      <c r="AB712" s="61"/>
+      <c r="AC712" s="61"/>
+      <c r="AD712" s="61"/>
+      <c r="AE712" s="61"/>
+      <c r="AF712" s="61"/>
+      <c r="AG712" s="61"/>
+      <c r="AH712" s="61"/>
     </row>
     <row r="887" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B887" s="62"/>
-      <c r="C887" s="62"/>
-      <c r="D887" s="62"/>
-      <c r="E887" s="62"/>
-      <c r="F887" s="62"/>
-      <c r="G887" s="62"/>
-      <c r="H887" s="62"/>
-      <c r="I887" s="62"/>
-      <c r="J887" s="62"/>
-      <c r="K887" s="62"/>
-      <c r="L887" s="62"/>
-      <c r="M887" s="62"/>
-      <c r="N887" s="62"/>
-      <c r="O887" s="62"/>
-      <c r="P887" s="62"/>
-      <c r="Q887" s="62"/>
-      <c r="R887" s="62"/>
-      <c r="S887" s="62"/>
-      <c r="T887" s="62"/>
-      <c r="U887" s="62"/>
-      <c r="V887" s="62"/>
-      <c r="W887" s="62"/>
-      <c r="X887" s="62"/>
-      <c r="Y887" s="62"/>
-      <c r="Z887" s="62"/>
-      <c r="AA887" s="62"/>
-      <c r="AB887" s="62"/>
-      <c r="AC887" s="62"/>
-      <c r="AD887" s="62"/>
-      <c r="AE887" s="62"/>
-      <c r="AF887" s="62"/>
-      <c r="AG887" s="62"/>
-      <c r="AH887" s="62"/>
+      <c r="B887" s="61"/>
+      <c r="C887" s="61"/>
+      <c r="D887" s="61"/>
+      <c r="E887" s="61"/>
+      <c r="F887" s="61"/>
+      <c r="G887" s="61"/>
+      <c r="H887" s="61"/>
+      <c r="I887" s="61"/>
+      <c r="J887" s="61"/>
+      <c r="K887" s="61"/>
+      <c r="L887" s="61"/>
+      <c r="M887" s="61"/>
+      <c r="N887" s="61"/>
+      <c r="O887" s="61"/>
+      <c r="P887" s="61"/>
+      <c r="Q887" s="61"/>
+      <c r="R887" s="61"/>
+      <c r="S887" s="61"/>
+      <c r="T887" s="61"/>
+      <c r="U887" s="61"/>
+      <c r="V887" s="61"/>
+      <c r="W887" s="61"/>
+      <c r="X887" s="61"/>
+      <c r="Y887" s="61"/>
+      <c r="Z887" s="61"/>
+      <c r="AA887" s="61"/>
+      <c r="AB887" s="61"/>
+      <c r="AC887" s="61"/>
+      <c r="AD887" s="61"/>
+      <c r="AE887" s="61"/>
+      <c r="AF887" s="61"/>
+      <c r="AG887" s="61"/>
+      <c r="AH887" s="61"/>
     </row>
     <row r="1100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1100" s="62"/>
-      <c r="C1100" s="62"/>
-      <c r="D1100" s="62"/>
-      <c r="E1100" s="62"/>
-      <c r="F1100" s="62"/>
-      <c r="G1100" s="62"/>
-      <c r="H1100" s="62"/>
-      <c r="I1100" s="62"/>
-      <c r="J1100" s="62"/>
-      <c r="K1100" s="62"/>
-      <c r="L1100" s="62"/>
-      <c r="M1100" s="62"/>
-      <c r="N1100" s="62"/>
-      <c r="O1100" s="62"/>
-      <c r="P1100" s="62"/>
-      <c r="Q1100" s="62"/>
-      <c r="R1100" s="62"/>
-      <c r="S1100" s="62"/>
-      <c r="T1100" s="62"/>
-      <c r="U1100" s="62"/>
-      <c r="V1100" s="62"/>
-      <c r="W1100" s="62"/>
-      <c r="X1100" s="62"/>
-      <c r="Y1100" s="62"/>
-      <c r="Z1100" s="62"/>
-      <c r="AA1100" s="62"/>
-      <c r="AB1100" s="62"/>
-      <c r="AC1100" s="62"/>
-      <c r="AD1100" s="62"/>
-      <c r="AE1100" s="62"/>
-      <c r="AF1100" s="62"/>
-      <c r="AG1100" s="62"/>
-      <c r="AH1100" s="62"/>
+      <c r="B1100" s="61"/>
+      <c r="C1100" s="61"/>
+      <c r="D1100" s="61"/>
+      <c r="E1100" s="61"/>
+      <c r="F1100" s="61"/>
+      <c r="G1100" s="61"/>
+      <c r="H1100" s="61"/>
+      <c r="I1100" s="61"/>
+      <c r="J1100" s="61"/>
+      <c r="K1100" s="61"/>
+      <c r="L1100" s="61"/>
+      <c r="M1100" s="61"/>
+      <c r="N1100" s="61"/>
+      <c r="O1100" s="61"/>
+      <c r="P1100" s="61"/>
+      <c r="Q1100" s="61"/>
+      <c r="R1100" s="61"/>
+      <c r="S1100" s="61"/>
+      <c r="T1100" s="61"/>
+      <c r="U1100" s="61"/>
+      <c r="V1100" s="61"/>
+      <c r="W1100" s="61"/>
+      <c r="X1100" s="61"/>
+      <c r="Y1100" s="61"/>
+      <c r="Z1100" s="61"/>
+      <c r="AA1100" s="61"/>
+      <c r="AB1100" s="61"/>
+      <c r="AC1100" s="61"/>
+      <c r="AD1100" s="61"/>
+      <c r="AE1100" s="61"/>
+      <c r="AF1100" s="61"/>
+      <c r="AG1100" s="61"/>
+      <c r="AH1100" s="61"/>
     </row>
     <row r="1227" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1227" s="62"/>
-      <c r="C1227" s="62"/>
-      <c r="D1227" s="62"/>
-      <c r="E1227" s="62"/>
-      <c r="F1227" s="62"/>
-      <c r="G1227" s="62"/>
-      <c r="H1227" s="62"/>
-      <c r="I1227" s="62"/>
-      <c r="J1227" s="62"/>
-      <c r="K1227" s="62"/>
-      <c r="L1227" s="62"/>
-      <c r="M1227" s="62"/>
-      <c r="N1227" s="62"/>
-      <c r="O1227" s="62"/>
-      <c r="P1227" s="62"/>
-      <c r="Q1227" s="62"/>
-      <c r="R1227" s="62"/>
-      <c r="S1227" s="62"/>
-      <c r="T1227" s="62"/>
-      <c r="U1227" s="62"/>
-      <c r="V1227" s="62"/>
-      <c r="W1227" s="62"/>
-      <c r="X1227" s="62"/>
-      <c r="Y1227" s="62"/>
-      <c r="Z1227" s="62"/>
-      <c r="AA1227" s="62"/>
-      <c r="AB1227" s="62"/>
-      <c r="AC1227" s="62"/>
-      <c r="AD1227" s="62"/>
-      <c r="AE1227" s="62"/>
-      <c r="AF1227" s="62"/>
-      <c r="AG1227" s="62"/>
-      <c r="AH1227" s="62"/>
+      <c r="B1227" s="61"/>
+      <c r="C1227" s="61"/>
+      <c r="D1227" s="61"/>
+      <c r="E1227" s="61"/>
+      <c r="F1227" s="61"/>
+      <c r="G1227" s="61"/>
+      <c r="H1227" s="61"/>
+      <c r="I1227" s="61"/>
+      <c r="J1227" s="61"/>
+      <c r="K1227" s="61"/>
+      <c r="L1227" s="61"/>
+      <c r="M1227" s="61"/>
+      <c r="N1227" s="61"/>
+      <c r="O1227" s="61"/>
+      <c r="P1227" s="61"/>
+      <c r="Q1227" s="61"/>
+      <c r="R1227" s="61"/>
+      <c r="S1227" s="61"/>
+      <c r="T1227" s="61"/>
+      <c r="U1227" s="61"/>
+      <c r="V1227" s="61"/>
+      <c r="W1227" s="61"/>
+      <c r="X1227" s="61"/>
+      <c r="Y1227" s="61"/>
+      <c r="Z1227" s="61"/>
+      <c r="AA1227" s="61"/>
+      <c r="AB1227" s="61"/>
+      <c r="AC1227" s="61"/>
+      <c r="AD1227" s="61"/>
+      <c r="AE1227" s="61"/>
+      <c r="AF1227" s="61"/>
+      <c r="AG1227" s="61"/>
+      <c r="AH1227" s="61"/>
     </row>
     <row r="1390" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1390" s="62"/>
-      <c r="C1390" s="62"/>
-      <c r="D1390" s="62"/>
-      <c r="E1390" s="62"/>
-      <c r="F1390" s="62"/>
-      <c r="G1390" s="62"/>
-      <c r="H1390" s="62"/>
-      <c r="I1390" s="62"/>
-      <c r="J1390" s="62"/>
-      <c r="K1390" s="62"/>
-      <c r="L1390" s="62"/>
-      <c r="M1390" s="62"/>
-      <c r="N1390" s="62"/>
-      <c r="O1390" s="62"/>
-      <c r="P1390" s="62"/>
-      <c r="Q1390" s="62"/>
-      <c r="R1390" s="62"/>
-      <c r="S1390" s="62"/>
-      <c r="T1390" s="62"/>
-      <c r="U1390" s="62"/>
-      <c r="V1390" s="62"/>
-      <c r="W1390" s="62"/>
-      <c r="X1390" s="62"/>
-      <c r="Y1390" s="62"/>
-      <c r="Z1390" s="62"/>
-      <c r="AA1390" s="62"/>
-      <c r="AB1390" s="62"/>
-      <c r="AC1390" s="62"/>
-      <c r="AD1390" s="62"/>
-      <c r="AE1390" s="62"/>
-      <c r="AF1390" s="62"/>
-      <c r="AG1390" s="62"/>
-      <c r="AH1390" s="62"/>
+      <c r="B1390" s="61"/>
+      <c r="C1390" s="61"/>
+      <c r="D1390" s="61"/>
+      <c r="E1390" s="61"/>
+      <c r="F1390" s="61"/>
+      <c r="G1390" s="61"/>
+      <c r="H1390" s="61"/>
+      <c r="I1390" s="61"/>
+      <c r="J1390" s="61"/>
+      <c r="K1390" s="61"/>
+      <c r="L1390" s="61"/>
+      <c r="M1390" s="61"/>
+      <c r="N1390" s="61"/>
+      <c r="O1390" s="61"/>
+      <c r="P1390" s="61"/>
+      <c r="Q1390" s="61"/>
+      <c r="R1390" s="61"/>
+      <c r="S1390" s="61"/>
+      <c r="T1390" s="61"/>
+      <c r="U1390" s="61"/>
+      <c r="V1390" s="61"/>
+      <c r="W1390" s="61"/>
+      <c r="X1390" s="61"/>
+      <c r="Y1390" s="61"/>
+      <c r="Z1390" s="61"/>
+      <c r="AA1390" s="61"/>
+      <c r="AB1390" s="61"/>
+      <c r="AC1390" s="61"/>
+      <c r="AD1390" s="61"/>
+      <c r="AE1390" s="61"/>
+      <c r="AF1390" s="61"/>
+      <c r="AG1390" s="61"/>
+      <c r="AH1390" s="61"/>
     </row>
     <row r="1502" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1502" s="62"/>
-      <c r="C1502" s="62"/>
-      <c r="D1502" s="62"/>
-      <c r="E1502" s="62"/>
-      <c r="F1502" s="62"/>
-      <c r="G1502" s="62"/>
-      <c r="H1502" s="62"/>
-      <c r="I1502" s="62"/>
-      <c r="J1502" s="62"/>
-      <c r="K1502" s="62"/>
-      <c r="L1502" s="62"/>
-      <c r="M1502" s="62"/>
-      <c r="N1502" s="62"/>
-      <c r="O1502" s="62"/>
-      <c r="P1502" s="62"/>
-      <c r="Q1502" s="62"/>
-      <c r="R1502" s="62"/>
-      <c r="S1502" s="62"/>
-      <c r="T1502" s="62"/>
-      <c r="U1502" s="62"/>
-      <c r="V1502" s="62"/>
-      <c r="W1502" s="62"/>
-      <c r="X1502" s="62"/>
-      <c r="Y1502" s="62"/>
-      <c r="Z1502" s="62"/>
-      <c r="AA1502" s="62"/>
-      <c r="AB1502" s="62"/>
-      <c r="AC1502" s="62"/>
-      <c r="AD1502" s="62"/>
-      <c r="AE1502" s="62"/>
-      <c r="AF1502" s="62"/>
-      <c r="AG1502" s="62"/>
-      <c r="AH1502" s="62"/>
+      <c r="B1502" s="61"/>
+      <c r="C1502" s="61"/>
+      <c r="D1502" s="61"/>
+      <c r="E1502" s="61"/>
+      <c r="F1502" s="61"/>
+      <c r="G1502" s="61"/>
+      <c r="H1502" s="61"/>
+      <c r="I1502" s="61"/>
+      <c r="J1502" s="61"/>
+      <c r="K1502" s="61"/>
+      <c r="L1502" s="61"/>
+      <c r="M1502" s="61"/>
+      <c r="N1502" s="61"/>
+      <c r="O1502" s="61"/>
+      <c r="P1502" s="61"/>
+      <c r="Q1502" s="61"/>
+      <c r="R1502" s="61"/>
+      <c r="S1502" s="61"/>
+      <c r="T1502" s="61"/>
+      <c r="U1502" s="61"/>
+      <c r="V1502" s="61"/>
+      <c r="W1502" s="61"/>
+      <c r="X1502" s="61"/>
+      <c r="Y1502" s="61"/>
+      <c r="Z1502" s="61"/>
+      <c r="AA1502" s="61"/>
+      <c r="AB1502" s="61"/>
+      <c r="AC1502" s="61"/>
+      <c r="AD1502" s="61"/>
+      <c r="AE1502" s="61"/>
+      <c r="AF1502" s="61"/>
+      <c r="AG1502" s="61"/>
+      <c r="AH1502" s="61"/>
     </row>
     <row r="1604" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1604" s="62"/>
-      <c r="C1604" s="62"/>
-      <c r="D1604" s="62"/>
-      <c r="E1604" s="62"/>
-      <c r="F1604" s="62"/>
-      <c r="G1604" s="62"/>
-      <c r="H1604" s="62"/>
-      <c r="I1604" s="62"/>
-      <c r="J1604" s="62"/>
-      <c r="K1604" s="62"/>
-      <c r="L1604" s="62"/>
-      <c r="M1604" s="62"/>
-      <c r="N1604" s="62"/>
-      <c r="O1604" s="62"/>
-      <c r="P1604" s="62"/>
-      <c r="Q1604" s="62"/>
-      <c r="R1604" s="62"/>
-      <c r="S1604" s="62"/>
-      <c r="T1604" s="62"/>
-      <c r="U1604" s="62"/>
-      <c r="V1604" s="62"/>
-      <c r="W1604" s="62"/>
-      <c r="X1604" s="62"/>
-      <c r="Y1604" s="62"/>
-      <c r="Z1604" s="62"/>
-      <c r="AA1604" s="62"/>
-      <c r="AB1604" s="62"/>
-      <c r="AC1604" s="62"/>
-      <c r="AD1604" s="62"/>
-      <c r="AE1604" s="62"/>
-      <c r="AF1604" s="62"/>
-      <c r="AG1604" s="62"/>
-      <c r="AH1604" s="62"/>
+      <c r="B1604" s="61"/>
+      <c r="C1604" s="61"/>
+      <c r="D1604" s="61"/>
+      <c r="E1604" s="61"/>
+      <c r="F1604" s="61"/>
+      <c r="G1604" s="61"/>
+      <c r="H1604" s="61"/>
+      <c r="I1604" s="61"/>
+      <c r="J1604" s="61"/>
+      <c r="K1604" s="61"/>
+      <c r="L1604" s="61"/>
+      <c r="M1604" s="61"/>
+      <c r="N1604" s="61"/>
+      <c r="O1604" s="61"/>
+      <c r="P1604" s="61"/>
+      <c r="Q1604" s="61"/>
+      <c r="R1604" s="61"/>
+      <c r="S1604" s="61"/>
+      <c r="T1604" s="61"/>
+      <c r="U1604" s="61"/>
+      <c r="V1604" s="61"/>
+      <c r="W1604" s="61"/>
+      <c r="X1604" s="61"/>
+      <c r="Y1604" s="61"/>
+      <c r="Z1604" s="61"/>
+      <c r="AA1604" s="61"/>
+      <c r="AB1604" s="61"/>
+      <c r="AC1604" s="61"/>
+      <c r="AD1604" s="61"/>
+      <c r="AE1604" s="61"/>
+      <c r="AF1604" s="61"/>
+      <c r="AG1604" s="61"/>
+      <c r="AH1604" s="61"/>
     </row>
     <row r="1698" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1698" s="62"/>
-      <c r="C1698" s="62"/>
-      <c r="D1698" s="62"/>
-      <c r="E1698" s="62"/>
-      <c r="F1698" s="62"/>
-      <c r="G1698" s="62"/>
-      <c r="H1698" s="62"/>
-      <c r="I1698" s="62"/>
-      <c r="J1698" s="62"/>
-      <c r="K1698" s="62"/>
-      <c r="L1698" s="62"/>
-      <c r="M1698" s="62"/>
-      <c r="N1698" s="62"/>
-      <c r="O1698" s="62"/>
-      <c r="P1698" s="62"/>
-      <c r="Q1698" s="62"/>
-      <c r="R1698" s="62"/>
-      <c r="S1698" s="62"/>
-      <c r="T1698" s="62"/>
-      <c r="U1698" s="62"/>
-      <c r="V1698" s="62"/>
-      <c r="W1698" s="62"/>
-      <c r="X1698" s="62"/>
-      <c r="Y1698" s="62"/>
-      <c r="Z1698" s="62"/>
-      <c r="AA1698" s="62"/>
-      <c r="AB1698" s="62"/>
-      <c r="AC1698" s="62"/>
-      <c r="AD1698" s="62"/>
-      <c r="AE1698" s="62"/>
-      <c r="AF1698" s="62"/>
-      <c r="AG1698" s="62"/>
-      <c r="AH1698" s="62"/>
+      <c r="B1698" s="61"/>
+      <c r="C1698" s="61"/>
+      <c r="D1698" s="61"/>
+      <c r="E1698" s="61"/>
+      <c r="F1698" s="61"/>
+      <c r="G1698" s="61"/>
+      <c r="H1698" s="61"/>
+      <c r="I1698" s="61"/>
+      <c r="J1698" s="61"/>
+      <c r="K1698" s="61"/>
+      <c r="L1698" s="61"/>
+      <c r="M1698" s="61"/>
+      <c r="N1698" s="61"/>
+      <c r="O1698" s="61"/>
+      <c r="P1698" s="61"/>
+      <c r="Q1698" s="61"/>
+      <c r="R1698" s="61"/>
+      <c r="S1698" s="61"/>
+      <c r="T1698" s="61"/>
+      <c r="U1698" s="61"/>
+      <c r="V1698" s="61"/>
+      <c r="W1698" s="61"/>
+      <c r="X1698" s="61"/>
+      <c r="Y1698" s="61"/>
+      <c r="Z1698" s="61"/>
+      <c r="AA1698" s="61"/>
+      <c r="AB1698" s="61"/>
+      <c r="AC1698" s="61"/>
+      <c r="AD1698" s="61"/>
+      <c r="AE1698" s="61"/>
+      <c r="AF1698" s="61"/>
+      <c r="AG1698" s="61"/>
+      <c r="AH1698" s="61"/>
     </row>
     <row r="1945" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1945" s="62"/>
-      <c r="C1945" s="62"/>
-      <c r="D1945" s="62"/>
-      <c r="E1945" s="62"/>
-      <c r="F1945" s="62"/>
-      <c r="G1945" s="62"/>
-      <c r="H1945" s="62"/>
-      <c r="I1945" s="62"/>
-      <c r="J1945" s="62"/>
-      <c r="K1945" s="62"/>
-      <c r="L1945" s="62"/>
-      <c r="M1945" s="62"/>
-      <c r="N1945" s="62"/>
-      <c r="O1945" s="62"/>
-      <c r="P1945" s="62"/>
-      <c r="Q1945" s="62"/>
-      <c r="R1945" s="62"/>
-      <c r="S1945" s="62"/>
-      <c r="T1945" s="62"/>
-      <c r="U1945" s="62"/>
-      <c r="V1945" s="62"/>
-      <c r="W1945" s="62"/>
-      <c r="X1945" s="62"/>
-      <c r="Y1945" s="62"/>
-      <c r="Z1945" s="62"/>
-      <c r="AA1945" s="62"/>
-      <c r="AB1945" s="62"/>
-      <c r="AC1945" s="62"/>
-      <c r="AD1945" s="62"/>
-      <c r="AE1945" s="62"/>
-      <c r="AF1945" s="62"/>
-      <c r="AG1945" s="62"/>
-      <c r="AH1945" s="62"/>
+      <c r="B1945" s="61"/>
+      <c r="C1945" s="61"/>
+      <c r="D1945" s="61"/>
+      <c r="E1945" s="61"/>
+      <c r="F1945" s="61"/>
+      <c r="G1945" s="61"/>
+      <c r="H1945" s="61"/>
+      <c r="I1945" s="61"/>
+      <c r="J1945" s="61"/>
+      <c r="K1945" s="61"/>
+      <c r="L1945" s="61"/>
+      <c r="M1945" s="61"/>
+      <c r="N1945" s="61"/>
+      <c r="O1945" s="61"/>
+      <c r="P1945" s="61"/>
+      <c r="Q1945" s="61"/>
+      <c r="R1945" s="61"/>
+      <c r="S1945" s="61"/>
+      <c r="T1945" s="61"/>
+      <c r="U1945" s="61"/>
+      <c r="V1945" s="61"/>
+      <c r="W1945" s="61"/>
+      <c r="X1945" s="61"/>
+      <c r="Y1945" s="61"/>
+      <c r="Z1945" s="61"/>
+      <c r="AA1945" s="61"/>
+      <c r="AB1945" s="61"/>
+      <c r="AC1945" s="61"/>
+      <c r="AD1945" s="61"/>
+      <c r="AE1945" s="61"/>
+      <c r="AF1945" s="61"/>
+      <c r="AG1945" s="61"/>
+      <c r="AH1945" s="61"/>
     </row>
     <row r="2031" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2031" s="62"/>
-      <c r="C2031" s="62"/>
-      <c r="D2031" s="62"/>
-      <c r="E2031" s="62"/>
-      <c r="F2031" s="62"/>
-      <c r="G2031" s="62"/>
-      <c r="H2031" s="62"/>
-      <c r="I2031" s="62"/>
-      <c r="J2031" s="62"/>
-      <c r="K2031" s="62"/>
-      <c r="L2031" s="62"/>
-      <c r="M2031" s="62"/>
-      <c r="N2031" s="62"/>
-      <c r="O2031" s="62"/>
-      <c r="P2031" s="62"/>
-      <c r="Q2031" s="62"/>
-      <c r="R2031" s="62"/>
-      <c r="S2031" s="62"/>
-      <c r="T2031" s="62"/>
-      <c r="U2031" s="62"/>
-      <c r="V2031" s="62"/>
-      <c r="W2031" s="62"/>
-      <c r="X2031" s="62"/>
-      <c r="Y2031" s="62"/>
-      <c r="Z2031" s="62"/>
-      <c r="AA2031" s="62"/>
-      <c r="AB2031" s="62"/>
-      <c r="AC2031" s="62"/>
-      <c r="AD2031" s="62"/>
-      <c r="AE2031" s="62"/>
-      <c r="AF2031" s="62"/>
-      <c r="AG2031" s="62"/>
-      <c r="AH2031" s="62"/>
+      <c r="B2031" s="61"/>
+      <c r="C2031" s="61"/>
+      <c r="D2031" s="61"/>
+      <c r="E2031" s="61"/>
+      <c r="F2031" s="61"/>
+      <c r="G2031" s="61"/>
+      <c r="H2031" s="61"/>
+      <c r="I2031" s="61"/>
+      <c r="J2031" s="61"/>
+      <c r="K2031" s="61"/>
+      <c r="L2031" s="61"/>
+      <c r="M2031" s="61"/>
+      <c r="N2031" s="61"/>
+      <c r="O2031" s="61"/>
+      <c r="P2031" s="61"/>
+      <c r="Q2031" s="61"/>
+      <c r="R2031" s="61"/>
+      <c r="S2031" s="61"/>
+      <c r="T2031" s="61"/>
+      <c r="U2031" s="61"/>
+      <c r="V2031" s="61"/>
+      <c r="W2031" s="61"/>
+      <c r="X2031" s="61"/>
+      <c r="Y2031" s="61"/>
+      <c r="Z2031" s="61"/>
+      <c r="AA2031" s="61"/>
+      <c r="AB2031" s="61"/>
+      <c r="AC2031" s="61"/>
+      <c r="AD2031" s="61"/>
+      <c r="AE2031" s="61"/>
+      <c r="AF2031" s="61"/>
+      <c r="AG2031" s="61"/>
+      <c r="AH2031" s="61"/>
     </row>
     <row r="2153" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2153" s="62"/>
-      <c r="C2153" s="62"/>
-      <c r="D2153" s="62"/>
-      <c r="E2153" s="62"/>
-      <c r="F2153" s="62"/>
-      <c r="G2153" s="62"/>
-      <c r="H2153" s="62"/>
-      <c r="I2153" s="62"/>
-      <c r="J2153" s="62"/>
-      <c r="K2153" s="62"/>
-      <c r="L2153" s="62"/>
-      <c r="M2153" s="62"/>
-      <c r="N2153" s="62"/>
-      <c r="O2153" s="62"/>
-      <c r="P2153" s="62"/>
-      <c r="Q2153" s="62"/>
-      <c r="R2153" s="62"/>
-      <c r="S2153" s="62"/>
-      <c r="T2153" s="62"/>
-      <c r="U2153" s="62"/>
-      <c r="V2153" s="62"/>
-      <c r="W2153" s="62"/>
-      <c r="X2153" s="62"/>
-      <c r="Y2153" s="62"/>
-      <c r="Z2153" s="62"/>
-      <c r="AA2153" s="62"/>
-      <c r="AB2153" s="62"/>
-      <c r="AC2153" s="62"/>
-      <c r="AD2153" s="62"/>
-      <c r="AE2153" s="62"/>
-      <c r="AF2153" s="62"/>
-      <c r="AG2153" s="62"/>
-      <c r="AH2153" s="62"/>
+      <c r="B2153" s="61"/>
+      <c r="C2153" s="61"/>
+      <c r="D2153" s="61"/>
+      <c r="E2153" s="61"/>
+      <c r="F2153" s="61"/>
+      <c r="G2153" s="61"/>
+      <c r="H2153" s="61"/>
+      <c r="I2153" s="61"/>
+      <c r="J2153" s="61"/>
+      <c r="K2153" s="61"/>
+      <c r="L2153" s="61"/>
+      <c r="M2153" s="61"/>
+      <c r="N2153" s="61"/>
+      <c r="O2153" s="61"/>
+      <c r="P2153" s="61"/>
+      <c r="Q2153" s="61"/>
+      <c r="R2153" s="61"/>
+      <c r="S2153" s="61"/>
+      <c r="T2153" s="61"/>
+      <c r="U2153" s="61"/>
+      <c r="V2153" s="61"/>
+      <c r="W2153" s="61"/>
+      <c r="X2153" s="61"/>
+      <c r="Y2153" s="61"/>
+      <c r="Z2153" s="61"/>
+      <c r="AA2153" s="61"/>
+      <c r="AB2153" s="61"/>
+      <c r="AC2153" s="61"/>
+      <c r="AD2153" s="61"/>
+      <c r="AE2153" s="61"/>
+      <c r="AF2153" s="61"/>
+      <c r="AG2153" s="61"/>
+      <c r="AH2153" s="61"/>
     </row>
     <row r="2317" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2317" s="62"/>
-      <c r="C2317" s="62"/>
-      <c r="D2317" s="62"/>
-      <c r="E2317" s="62"/>
-      <c r="F2317" s="62"/>
-      <c r="G2317" s="62"/>
-      <c r="H2317" s="62"/>
-      <c r="I2317" s="62"/>
-      <c r="J2317" s="62"/>
-      <c r="K2317" s="62"/>
-      <c r="L2317" s="62"/>
-      <c r="M2317" s="62"/>
-      <c r="N2317" s="62"/>
-      <c r="O2317" s="62"/>
-      <c r="P2317" s="62"/>
-      <c r="Q2317" s="62"/>
-      <c r="R2317" s="62"/>
-      <c r="S2317" s="62"/>
-      <c r="T2317" s="62"/>
-      <c r="U2317" s="62"/>
-      <c r="V2317" s="62"/>
-      <c r="W2317" s="62"/>
-      <c r="X2317" s="62"/>
-      <c r="Y2317" s="62"/>
-      <c r="Z2317" s="62"/>
-      <c r="AA2317" s="62"/>
-      <c r="AB2317" s="62"/>
-      <c r="AC2317" s="62"/>
-      <c r="AD2317" s="62"/>
-      <c r="AE2317" s="62"/>
-      <c r="AF2317" s="62"/>
-      <c r="AG2317" s="62"/>
-      <c r="AH2317" s="62"/>
+      <c r="B2317" s="61"/>
+      <c r="C2317" s="61"/>
+      <c r="D2317" s="61"/>
+      <c r="E2317" s="61"/>
+      <c r="F2317" s="61"/>
+      <c r="G2317" s="61"/>
+      <c r="H2317" s="61"/>
+      <c r="I2317" s="61"/>
+      <c r="J2317" s="61"/>
+      <c r="K2317" s="61"/>
+      <c r="L2317" s="61"/>
+      <c r="M2317" s="61"/>
+      <c r="N2317" s="61"/>
+      <c r="O2317" s="61"/>
+      <c r="P2317" s="61"/>
+      <c r="Q2317" s="61"/>
+      <c r="R2317" s="61"/>
+      <c r="S2317" s="61"/>
+      <c r="T2317" s="61"/>
+      <c r="U2317" s="61"/>
+      <c r="V2317" s="61"/>
+      <c r="W2317" s="61"/>
+      <c r="X2317" s="61"/>
+      <c r="Y2317" s="61"/>
+      <c r="Z2317" s="61"/>
+      <c r="AA2317" s="61"/>
+      <c r="AB2317" s="61"/>
+      <c r="AC2317" s="61"/>
+      <c r="AD2317" s="61"/>
+      <c r="AE2317" s="61"/>
+      <c r="AF2317" s="61"/>
+      <c r="AG2317" s="61"/>
+      <c r="AH2317" s="61"/>
     </row>
     <row r="2419" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2419" s="62"/>
-      <c r="C2419" s="62"/>
-      <c r="D2419" s="62"/>
-      <c r="E2419" s="62"/>
-      <c r="F2419" s="62"/>
-      <c r="G2419" s="62"/>
-      <c r="H2419" s="62"/>
-      <c r="I2419" s="62"/>
-      <c r="J2419" s="62"/>
-      <c r="K2419" s="62"/>
-      <c r="L2419" s="62"/>
-      <c r="M2419" s="62"/>
-      <c r="N2419" s="62"/>
-      <c r="O2419" s="62"/>
-      <c r="P2419" s="62"/>
-      <c r="Q2419" s="62"/>
-      <c r="R2419" s="62"/>
-      <c r="S2419" s="62"/>
-      <c r="T2419" s="62"/>
-      <c r="U2419" s="62"/>
-      <c r="V2419" s="62"/>
-      <c r="W2419" s="62"/>
-      <c r="X2419" s="62"/>
-      <c r="Y2419" s="62"/>
-      <c r="Z2419" s="62"/>
-      <c r="AA2419" s="62"/>
-      <c r="AB2419" s="62"/>
-      <c r="AC2419" s="62"/>
-      <c r="AD2419" s="62"/>
-      <c r="AE2419" s="62"/>
-      <c r="AF2419" s="62"/>
-      <c r="AG2419" s="62"/>
-      <c r="AH2419" s="62"/>
+      <c r="B2419" s="61"/>
+      <c r="C2419" s="61"/>
+      <c r="D2419" s="61"/>
+      <c r="E2419" s="61"/>
+      <c r="F2419" s="61"/>
+      <c r="G2419" s="61"/>
+      <c r="H2419" s="61"/>
+      <c r="I2419" s="61"/>
+      <c r="J2419" s="61"/>
+      <c r="K2419" s="61"/>
+      <c r="L2419" s="61"/>
+      <c r="M2419" s="61"/>
+      <c r="N2419" s="61"/>
+      <c r="O2419" s="61"/>
+      <c r="P2419" s="61"/>
+      <c r="Q2419" s="61"/>
+      <c r="R2419" s="61"/>
+      <c r="S2419" s="61"/>
+      <c r="T2419" s="61"/>
+      <c r="U2419" s="61"/>
+      <c r="V2419" s="61"/>
+      <c r="W2419" s="61"/>
+      <c r="X2419" s="61"/>
+      <c r="Y2419" s="61"/>
+      <c r="Z2419" s="61"/>
+      <c r="AA2419" s="61"/>
+      <c r="AB2419" s="61"/>
+      <c r="AC2419" s="61"/>
+      <c r="AD2419" s="61"/>
+      <c r="AE2419" s="61"/>
+      <c r="AF2419" s="61"/>
+      <c r="AG2419" s="61"/>
+      <c r="AH2419" s="61"/>
     </row>
     <row r="2509" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2509" s="62"/>
-      <c r="C2509" s="62"/>
-      <c r="D2509" s="62"/>
-      <c r="E2509" s="62"/>
-      <c r="F2509" s="62"/>
-      <c r="G2509" s="62"/>
-      <c r="H2509" s="62"/>
-      <c r="I2509" s="62"/>
-      <c r="J2509" s="62"/>
-      <c r="K2509" s="62"/>
-      <c r="L2509" s="62"/>
-      <c r="M2509" s="62"/>
-      <c r="N2509" s="62"/>
-      <c r="O2509" s="62"/>
-      <c r="P2509" s="62"/>
-      <c r="Q2509" s="62"/>
-      <c r="R2509" s="62"/>
-      <c r="S2509" s="62"/>
-      <c r="T2509" s="62"/>
-      <c r="U2509" s="62"/>
-      <c r="V2509" s="62"/>
-      <c r="W2509" s="62"/>
-      <c r="X2509" s="62"/>
-      <c r="Y2509" s="62"/>
-      <c r="Z2509" s="62"/>
-      <c r="AA2509" s="62"/>
-      <c r="AB2509" s="62"/>
-      <c r="AC2509" s="62"/>
-      <c r="AD2509" s="62"/>
-      <c r="AE2509" s="62"/>
-      <c r="AF2509" s="62"/>
-      <c r="AG2509" s="62"/>
-      <c r="AH2509" s="62"/>
+      <c r="B2509" s="61"/>
+      <c r="C2509" s="61"/>
+      <c r="D2509" s="61"/>
+      <c r="E2509" s="61"/>
+      <c r="F2509" s="61"/>
+      <c r="G2509" s="61"/>
+      <c r="H2509" s="61"/>
+      <c r="I2509" s="61"/>
+      <c r="J2509" s="61"/>
+      <c r="K2509" s="61"/>
+      <c r="L2509" s="61"/>
+      <c r="M2509" s="61"/>
+      <c r="N2509" s="61"/>
+      <c r="O2509" s="61"/>
+      <c r="P2509" s="61"/>
+      <c r="Q2509" s="61"/>
+      <c r="R2509" s="61"/>
+      <c r="S2509" s="61"/>
+      <c r="T2509" s="61"/>
+      <c r="U2509" s="61"/>
+      <c r="V2509" s="61"/>
+      <c r="W2509" s="61"/>
+      <c r="X2509" s="61"/>
+      <c r="Y2509" s="61"/>
+      <c r="Z2509" s="61"/>
+      <c r="AA2509" s="61"/>
+      <c r="AB2509" s="61"/>
+      <c r="AC2509" s="61"/>
+      <c r="AD2509" s="61"/>
+      <c r="AE2509" s="61"/>
+      <c r="AF2509" s="61"/>
+      <c r="AG2509" s="61"/>
+      <c r="AH2509" s="61"/>
     </row>
     <row r="2598" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2598" s="62"/>
-      <c r="C2598" s="62"/>
-      <c r="D2598" s="62"/>
-      <c r="E2598" s="62"/>
-      <c r="F2598" s="62"/>
-      <c r="G2598" s="62"/>
-      <c r="H2598" s="62"/>
-      <c r="I2598" s="62"/>
-      <c r="J2598" s="62"/>
-      <c r="K2598" s="62"/>
-      <c r="L2598" s="62"/>
-      <c r="M2598" s="62"/>
-      <c r="N2598" s="62"/>
-      <c r="O2598" s="62"/>
-      <c r="P2598" s="62"/>
-      <c r="Q2598" s="62"/>
-      <c r="R2598" s="62"/>
-      <c r="S2598" s="62"/>
-      <c r="T2598" s="62"/>
-      <c r="U2598" s="62"/>
-      <c r="V2598" s="62"/>
-      <c r="W2598" s="62"/>
-      <c r="X2598" s="62"/>
-      <c r="Y2598" s="62"/>
-      <c r="Z2598" s="62"/>
-      <c r="AA2598" s="62"/>
-      <c r="AB2598" s="62"/>
-      <c r="AC2598" s="62"/>
-      <c r="AD2598" s="62"/>
-      <c r="AE2598" s="62"/>
-      <c r="AF2598" s="62"/>
-      <c r="AG2598" s="62"/>
-      <c r="AH2598" s="62"/>
+      <c r="B2598" s="61"/>
+      <c r="C2598" s="61"/>
+      <c r="D2598" s="61"/>
+      <c r="E2598" s="61"/>
+      <c r="F2598" s="61"/>
+      <c r="G2598" s="61"/>
+      <c r="H2598" s="61"/>
+      <c r="I2598" s="61"/>
+      <c r="J2598" s="61"/>
+      <c r="K2598" s="61"/>
+      <c r="L2598" s="61"/>
+      <c r="M2598" s="61"/>
+      <c r="N2598" s="61"/>
+      <c r="O2598" s="61"/>
+      <c r="P2598" s="61"/>
+      <c r="Q2598" s="61"/>
+      <c r="R2598" s="61"/>
+      <c r="S2598" s="61"/>
+      <c r="T2598" s="61"/>
+      <c r="U2598" s="61"/>
+      <c r="V2598" s="61"/>
+      <c r="W2598" s="61"/>
+      <c r="X2598" s="61"/>
+      <c r="Y2598" s="61"/>
+      <c r="Z2598" s="61"/>
+      <c r="AA2598" s="61"/>
+      <c r="AB2598" s="61"/>
+      <c r="AC2598" s="61"/>
+      <c r="AD2598" s="61"/>
+      <c r="AE2598" s="61"/>
+      <c r="AF2598" s="61"/>
+      <c r="AG2598" s="61"/>
+      <c r="AH2598" s="61"/>
     </row>
     <row r="2719" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2719" s="62"/>
-      <c r="C2719" s="62"/>
-      <c r="D2719" s="62"/>
-      <c r="E2719" s="62"/>
-      <c r="F2719" s="62"/>
-      <c r="G2719" s="62"/>
-      <c r="H2719" s="62"/>
-      <c r="I2719" s="62"/>
-      <c r="J2719" s="62"/>
-      <c r="K2719" s="62"/>
-      <c r="L2719" s="62"/>
-      <c r="M2719" s="62"/>
-      <c r="N2719" s="62"/>
-      <c r="O2719" s="62"/>
-      <c r="P2719" s="62"/>
-      <c r="Q2719" s="62"/>
-      <c r="R2719" s="62"/>
-      <c r="S2719" s="62"/>
-      <c r="T2719" s="62"/>
-      <c r="U2719" s="62"/>
-      <c r="V2719" s="62"/>
-      <c r="W2719" s="62"/>
-      <c r="X2719" s="62"/>
-      <c r="Y2719" s="62"/>
-      <c r="Z2719" s="62"/>
-      <c r="AA2719" s="62"/>
-      <c r="AB2719" s="62"/>
-      <c r="AC2719" s="62"/>
-      <c r="AD2719" s="62"/>
-      <c r="AE2719" s="62"/>
-      <c r="AF2719" s="62"/>
-      <c r="AG2719" s="62"/>
-      <c r="AH2719" s="62"/>
+      <c r="B2719" s="61"/>
+      <c r="C2719" s="61"/>
+      <c r="D2719" s="61"/>
+      <c r="E2719" s="61"/>
+      <c r="F2719" s="61"/>
+      <c r="G2719" s="61"/>
+      <c r="H2719" s="61"/>
+      <c r="I2719" s="61"/>
+      <c r="J2719" s="61"/>
+      <c r="K2719" s="61"/>
+      <c r="L2719" s="61"/>
+      <c r="M2719" s="61"/>
+      <c r="N2719" s="61"/>
+      <c r="O2719" s="61"/>
+      <c r="P2719" s="61"/>
+      <c r="Q2719" s="61"/>
+      <c r="R2719" s="61"/>
+      <c r="S2719" s="61"/>
+      <c r="T2719" s="61"/>
+      <c r="U2719" s="61"/>
+      <c r="V2719" s="61"/>
+      <c r="W2719" s="61"/>
+      <c r="X2719" s="61"/>
+      <c r="Y2719" s="61"/>
+      <c r="Z2719" s="61"/>
+      <c r="AA2719" s="61"/>
+      <c r="AB2719" s="61"/>
+      <c r="AC2719" s="61"/>
+      <c r="AD2719" s="61"/>
+      <c r="AE2719" s="61"/>
+      <c r="AF2719" s="61"/>
+      <c r="AG2719" s="61"/>
+      <c r="AH2719" s="61"/>
     </row>
     <row r="2837" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2837" s="62"/>
-      <c r="C2837" s="62"/>
-      <c r="D2837" s="62"/>
-      <c r="E2837" s="62"/>
-      <c r="F2837" s="62"/>
-      <c r="G2837" s="62"/>
-      <c r="H2837" s="62"/>
-      <c r="I2837" s="62"/>
-      <c r="J2837" s="62"/>
-      <c r="K2837" s="62"/>
-      <c r="L2837" s="62"/>
-      <c r="M2837" s="62"/>
-      <c r="N2837" s="62"/>
-      <c r="O2837" s="62"/>
-      <c r="P2837" s="62"/>
-      <c r="Q2837" s="62"/>
-      <c r="R2837" s="62"/>
-      <c r="S2837" s="62"/>
-      <c r="T2837" s="62"/>
-      <c r="U2837" s="62"/>
-      <c r="V2837" s="62"/>
-      <c r="W2837" s="62"/>
-      <c r="X2837" s="62"/>
-      <c r="Y2837" s="62"/>
-      <c r="Z2837" s="62"/>
-      <c r="AA2837" s="62"/>
-      <c r="AB2837" s="62"/>
-      <c r="AC2837" s="62"/>
-      <c r="AD2837" s="62"/>
-      <c r="AE2837" s="62"/>
-      <c r="AF2837" s="62"/>
-      <c r="AG2837" s="62"/>
-      <c r="AH2837" s="62"/>
+      <c r="B2837" s="61"/>
+      <c r="C2837" s="61"/>
+      <c r="D2837" s="61"/>
+      <c r="E2837" s="61"/>
+      <c r="F2837" s="61"/>
+      <c r="G2837" s="61"/>
+      <c r="H2837" s="61"/>
+      <c r="I2837" s="61"/>
+      <c r="J2837" s="61"/>
+      <c r="K2837" s="61"/>
+      <c r="L2837" s="61"/>
+      <c r="M2837" s="61"/>
+      <c r="N2837" s="61"/>
+      <c r="O2837" s="61"/>
+      <c r="P2837" s="61"/>
+      <c r="Q2837" s="61"/>
+      <c r="R2837" s="61"/>
+      <c r="S2837" s="61"/>
+      <c r="T2837" s="61"/>
+      <c r="U2837" s="61"/>
+      <c r="V2837" s="61"/>
+      <c r="W2837" s="61"/>
+      <c r="X2837" s="61"/>
+      <c r="Y2837" s="61"/>
+      <c r="Z2837" s="61"/>
+      <c r="AA2837" s="61"/>
+      <c r="AB2837" s="61"/>
+      <c r="AC2837" s="61"/>
+      <c r="AD2837" s="61"/>
+      <c r="AE2837" s="61"/>
+      <c r="AF2837" s="61"/>
+      <c r="AG2837" s="61"/>
+      <c r="AH2837" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B112:AH112"/>
+    <mergeCell ref="B146:AG146"/>
+    <mergeCell ref="B308:AH308"/>
+    <mergeCell ref="B511:AH511"/>
+    <mergeCell ref="B712:AH712"/>
+    <mergeCell ref="B887:AH887"/>
+    <mergeCell ref="B1100:AH1100"/>
+    <mergeCell ref="B1227:AH1227"/>
+    <mergeCell ref="B1390:AH1390"/>
+    <mergeCell ref="B1502:AH1502"/>
+    <mergeCell ref="B1604:AH1604"/>
+    <mergeCell ref="B1698:AH1698"/>
+    <mergeCell ref="B1945:AH1945"/>
+    <mergeCell ref="B2031:AH2031"/>
+    <mergeCell ref="B2719:AH2719"/>
     <mergeCell ref="B2837:AH2837"/>
     <mergeCell ref="B2153:AH2153"/>
     <mergeCell ref="B2317:AH2317"/>
     <mergeCell ref="B2419:AH2419"/>
     <mergeCell ref="B2509:AH2509"/>
     <mergeCell ref="B2598:AH2598"/>
-    <mergeCell ref="B1604:AH1604"/>
-    <mergeCell ref="B1698:AH1698"/>
-    <mergeCell ref="B1945:AH1945"/>
-    <mergeCell ref="B2031:AH2031"/>
-    <mergeCell ref="B2719:AH2719"/>
-    <mergeCell ref="B887:AH887"/>
-    <mergeCell ref="B1100:AH1100"/>
-    <mergeCell ref="B1227:AH1227"/>
-    <mergeCell ref="B1390:AH1390"/>
-    <mergeCell ref="B1502:AH1502"/>
-    <mergeCell ref="B112:AH112"/>
-    <mergeCell ref="B146:AG146"/>
-    <mergeCell ref="B308:AH308"/>
-    <mergeCell ref="B511:AH511"/>
-    <mergeCell ref="B712:AH712"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -48728,6 +48350,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -48871,22 +48508,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECB31917-5064-4B77-B728-1073145DAAB0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBEE4980-405A-4047-9C31-692477979E44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87143F3-CC76-441D-8DA6-CB30E14E41B9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -48902,21 +48541,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBEE4980-405A-4047-9C31-692477979E44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECB31917-5064-4B77-B728-1073145DAAB0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>